--- a/dashboard-builder/Bluefield-Example-Inputs.xlsx
+++ b/dashboard-builder/Bluefield-Example-Inputs.xlsx
@@ -8,9 +8,10 @@
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
     <sheet name="Settings" sheetId="2" r:id="rId2"/>
     <sheet name="Charts" sheetId="3" r:id="rId3"/>
-    <sheet name="Table" sheetId="4" r:id="rId4"/>
-    <sheet name="Commentary" sheetId="5" r:id="rId5"/>
-    <sheet name="Side Table" sheetId="6" r:id="rId6"/>
+    <sheet name="Footnotes" sheetId="4" r:id="rId4"/>
+    <sheet name="Table" sheetId="5" r:id="rId5"/>
+    <sheet name="Commentary" sheetId="6" r:id="rId6"/>
+    <sheet name="Side Table" sheetId="7" r:id="rId7"/>
   </sheets>
 </workbook>
 </file>
@@ -156,7 +157,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="130" customWidth="1"/>
+    <col min="1" max="1" width="140" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -177,7 +178,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.  Fill in the Settings, Charts, Table, Commentary and Side Table tabs.  Blue text on yellow = inputs.</t>
+          <t xml:space="preserve">1.  Fill in the Settings, Charts, Footnotes, Table, Commentary and Side Table tabs.  Blue text on yellow = inputs.</t>
         </is>
       </c>
     </row>
@@ -191,7 +192,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.  Open "Dashboard Builder.html" in Edge or Chrome and drag this workbook onto the page.</t>
+          <t xml:space="preserve">3.  Open the Dashboard Builder page in Edge or Chrome and drag this workbook onto it.</t>
         </is>
       </c>
     </row>
@@ -220,69 +221,125 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Charts  -  one row per chart / component / year with Jan-Dec values.  Leave months blank where there is no data yet.</t>
+          <t xml:space="preserve">               "Current month" drives the month and YTD columns of the table.  Current-year chart values after it are not shown.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">               Each distinct "Chart" name becomes its own chart.  Rows with a "Component" (e.g. Contracted, Merchant) are stacked.</t>
+          <t xml:space="preserve">Charts  -  one row per chart / component / year with Jan-Dec values.  Leave months blank where there is no data yet.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">               Every chart shows the Current year and Prior year from Settings side by side, month by month.</t>
+          <t xml:space="preserve">               Each distinct "Chart" name becomes its own chart.  Rows with a "Component" (e.g. Contracted, Merchant) are stacked.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Table  -  any number of rows.  The variance is calculated for you; "Better When" sets whether it shows green or red.</t>
+          <t xml:space="preserve">               Every chart shows the Prior year and Current year from Settings side by side, month by month.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commentary  -  Heading + Text pairs for the bottom-right box.</t>
+          <t xml:space="preserve">               Enter full precision here (e.g. 3.92); the Decimals column only controls how the chart labels are rounded.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Side Table  -  a free-form grid for the bottom-right box.  Row 1 = column headers.  Values print exactly as they appear in Excel.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17"/>
+          <t xml:space="preserve">Footnotes  -  explain a month on a chart.  Leave "Chart" blank to mark that month on every chart.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">               The month label gets a small number and the note prints under the charts.</t>
+        </is>
+      </c>
+    </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tips</t>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Table  -  any number of rows.  The variance is calculated for you; "Better When" sets whether it shows green or red.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">-  Do not rename the tabs or the column headers in row 1.  You can add, delete or reorder rows freely.</t>
+          <t xml:space="preserve">               Put a chart name in "From Chart" to fill Month Actual and YTD Actual from the Charts tab automatically</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">-  Copy this workbook for each asset (one workbook = one dashboard).</t>
+          <t xml:space="preserve">               (add a "From Component" to use just one component, e.g. Contracted).  Leave "From Chart" blank to type the actuals yourself.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">               "YTD Method": Sum (default) adds the months up; Average averages them (use for percentages like capacity factor).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">               Month EV Case and YTD EV Case are always typed in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Commentary  -  Heading + Text pairs for the bottom-right box.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Side Table  -  a free-form grid for the bottom-right box.  Row 1 = column headers.  Values print exactly as they appear in Excel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tips</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-  Do not rename the tabs or the column headers in row 1.  You can add, delete or reorder rows freely.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-  Copy this workbook for each asset (one workbook = one dashboard).</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t xml:space="preserve">-  Your data never leaves your computer: the builder page reads the file locally in the browser.</t>
         </is>
@@ -299,7 +356,7 @@
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="70" customWidth="1"/>
-    <col min="3" max="3" width="70" customWidth="1"/>
+    <col min="3" max="3" width="90" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -420,271 +477,283 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chart section title</t>
+          <t xml:space="preserve">Current month</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Monthly Performance - 2026 vs. 2025</t>
+          <t xml:space="preserve">Aug</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Header above the charts.</t>
+          <t xml:space="preserve">The month being reported.  Drives Month Actual and YTD (Jan through this month) in the table.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Data labels</t>
+          <t xml:space="preserve">Chart section title</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">This year</t>
+          <t xml:space="preserve">Monthly Performance - 2026 vs. 2025</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Which bars get value labels: This year / Both years / None.</t>
+          <t xml:space="preserve">Header above the charts.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chart columns</t>
+          <t xml:space="preserve">Data labels</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Auto</t>
+          <t xml:space="preserve">This year</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Auto = 1 column for up to 3 charts, 2 columns for more.</t>
+          <t xml:space="preserve">Which bars get value labels: This year / Both years / None.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Table title</t>
+          <t xml:space="preserve">Chart columns</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Operating and Financial Performance vs. Budget - Monthly &amp; YTD</t>
+          <t xml:space="preserve">Auto</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Header above the comparison table.</t>
+          <t xml:space="preserve">Auto = 1 column for up to 3 charts, 2 columns for more.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Month heading</t>
+          <t xml:space="preserve">Table title</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">August</t>
+          <t xml:space="preserve">Operating and Financial Performance vs. EV Case - Monthly &amp; YTD</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heading over the monthly columns, e.g. August.</t>
+          <t xml:space="preserve">Header above the comparison table.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">YTD heading</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">YTD Through August</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Month heading</t>
+        </is>
+      </c>
+      <c r="B13" s="8"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heading over the year-to-date columns.</t>
+          <t xml:space="preserve">Heading over the monthly columns.  Leave blank to use the Current month (e.g. August).</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Actual label</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Actual</t>
-        </is>
-      </c>
+          <t xml:space="preserve">YTD heading</t>
+        </is>
+      </c>
+      <c r="B14" s="8"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Column label for actual values.</t>
+          <t xml:space="preserve">Heading over the year-to-date columns.  Leave blank for "YTD Through August".</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comparison label</t>
+          <t xml:space="preserve">Actual label</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Budget</t>
+          <t xml:space="preserve">Actual</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Column label for the comparison case (EV Case, Budget, Forecast...).</t>
+          <t xml:space="preserve">Column label for actual values.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Variance label</t>
+          <t xml:space="preserve">Comparison label</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Variance</t>
+          <t xml:space="preserve">EV Case</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Column label for the variance.</t>
+          <t xml:space="preserve">Column label for the comparison case (EV Case, Budget, Forecast...).</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Negative numbers</t>
+          <t xml:space="preserve">Variance label</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parentheses</t>
+          <t xml:space="preserve">Variance</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parentheses: (1.8)   Minus sign: -1.8</t>
+          <t xml:space="preserve">Column label for the variance.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Side panel type</t>
+          <t xml:space="preserve">Negative numbers</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commentary</t>
+          <t xml:space="preserve">Parentheses</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commentary / Table / Table + Commentary / None.</t>
+          <t xml:space="preserve">Parentheses: (1.8)   Minus sign: -1.8</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Side panel title</t>
+          <t xml:space="preserve">Side panel type</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maintenance Commentary</t>
+          <t xml:space="preserve">Commentary</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Header of the bottom-right box.</t>
+          <t xml:space="preserve">Commentary / Table / Table + Commentary / None.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Side panel width %</t>
-        </is>
-      </c>
-      <c r="B20" s="8">
-        <v>30</v>
+          <t xml:space="preserve">Side panel title</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Maintenance Commentary</t>
+        </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Width of the bottom-right box as a share of the page (15-50).</t>
+          <t xml:space="preserve">Header of the bottom-right box.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Footer</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sources: Bluefield monthly operating reports; 2026 budget model.  Fictional example data.</t>
-        </is>
+          <t xml:space="preserve">Side panel width %</t>
+        </is>
+      </c>
+      <c r="B21" s="8">
+        <v>30</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sources line at the bottom of the page.</t>
+          <t xml:space="preserve">Width of the bottom-right box as a share of the page (15-50).</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
+          <t xml:space="preserve">Footer</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sources: Bluefield monthly operating reports; 2026 EV Case model.  Fictional example data.</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sources line at the bottom of the page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
           <t xml:space="preserve">Page size</t>
         </is>
       </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="B23" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Letter</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Letter or A4 (always landscape).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B9">
+  <dataValidations count="6">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B8">
+      <formula1>"Jan,Feb,Mar,Apr,May,Jun,Jul,Aug,Sep,Oct,Nov,Dec"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B10">
       <formula1>"This year,Both years,None"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B10">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B11">
       <formula1>"Auto,1,2,3"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B17">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B18">
       <formula1>"Parentheses,Minus sign"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B18">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B19">
       <formula1>"Commentary,Table,Table + Commentary,None"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B22">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B23">
       <formula1>"Letter,A4"</formula1>
     </dataValidation>
   </dataValidations>
@@ -828,7 +897,7 @@
         <v>52.4</v>
       </c>
       <c r="K2" s="9">
-        <v>51.7</v>
+        <v>41.7</v>
       </c>
       <c r="L2" s="9">
         <v>47.2</v>
@@ -901,34 +970,34 @@
       <c r="D4" s="8">
         <v>1</v>
       </c>
-      <c r="E4" s="9">
-        <v>1.6</v>
-      </c>
-      <c r="F4" s="9">
-        <v>1.8</v>
-      </c>
-      <c r="G4" s="9">
-        <v>2.6</v>
-      </c>
-      <c r="H4" s="9">
-        <v>3</v>
-      </c>
-      <c r="I4" s="9">
-        <v>3.4</v>
-      </c>
-      <c r="J4" s="9">
-        <v>4.1</v>
-      </c>
-      <c r="K4" s="9">
-        <v>4.3</v>
-      </c>
-      <c r="L4" s="9">
-        <v>3.9</v>
-      </c>
-      <c r="M4" s="9"/>
-      <c r="N4" s="9"/>
-      <c r="O4" s="9"/>
-      <c r="P4" s="9"/>
+      <c r="E4" s="10">
+        <v>1.62</v>
+      </c>
+      <c r="F4" s="10">
+        <v>1.84</v>
+      </c>
+      <c r="G4" s="10">
+        <v>2.57</v>
+      </c>
+      <c r="H4" s="10">
+        <v>3.03</v>
+      </c>
+      <c r="I4" s="10">
+        <v>3.41</v>
+      </c>
+      <c r="J4" s="10">
+        <v>4.12</v>
+      </c>
+      <c r="K4" s="10">
+        <v>3.46</v>
+      </c>
+      <c r="L4" s="10">
+        <v>3.92</v>
+      </c>
+      <c r="M4" s="10"/>
+      <c r="N4" s="10"/>
+      <c r="O4" s="10"/>
+      <c r="P4" s="10"/>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
@@ -993,34 +1062,34 @@
       <c r="D6" s="8">
         <v>1</v>
       </c>
-      <c r="E6" s="9">
-        <v>-0.4</v>
-      </c>
-      <c r="F6" s="9">
-        <v>0.1</v>
-      </c>
-      <c r="G6" s="9">
-        <v>0.9</v>
-      </c>
-      <c r="H6" s="9">
-        <v>1.3</v>
-      </c>
-      <c r="I6" s="9">
-        <v>1.7</v>
-      </c>
-      <c r="J6" s="9">
-        <v>2.3</v>
-      </c>
-      <c r="K6" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="L6" s="9">
-        <v>2.1</v>
-      </c>
-      <c r="M6" s="9"/>
-      <c r="N6" s="9"/>
-      <c r="O6" s="9"/>
-      <c r="P6" s="9"/>
+      <c r="E6" s="10">
+        <v>-0.41</v>
+      </c>
+      <c r="F6" s="10">
+        <v>0.12</v>
+      </c>
+      <c r="G6" s="10">
+        <v>0.88</v>
+      </c>
+      <c r="H6" s="10">
+        <v>1.31</v>
+      </c>
+      <c r="I6" s="10">
+        <v>1.69</v>
+      </c>
+      <c r="J6" s="10">
+        <v>2.27</v>
+      </c>
+      <c r="K6" s="10">
+        <v>1.66</v>
+      </c>
+      <c r="L6" s="10">
+        <v>2.07</v>
+      </c>
+      <c r="M6" s="10"/>
+      <c r="N6" s="10"/>
+      <c r="O6" s="10"/>
+      <c r="P6" s="10"/>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
@@ -1081,246 +1150,77 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="26" customWidth="1"/>
-    <col min="2" max="2" width="8" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="10" customWidth="1"/>
-    <col min="5" max="5" width="13" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
-    <col min="7" max="7" width="7" customWidth="1"/>
-    <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="18" customWidth="1"/>
-    <col min="10" max="10" width="12" customWidth="1"/>
-    <col min="11" max="11" width="16" customWidth="1"/>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="100" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Metric</t>
+          <t xml:space="preserve">Chart</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prefix</t>
+          <t xml:space="preserve">Month</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Suffix</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Decimals</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Better When</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Variance As</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bold</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Month Actual</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Month Comparison</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">YTD Actual</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">YTD Comparison</t>
+          <t xml:space="preserve">Note</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Generation</t>
-        </is>
-      </c>
-      <c r="B2" s="8"/>
+      <c r="A2" s="8"/>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jul</t>
+        </is>
+      </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> GWh</t>
-        </is>
-      </c>
-      <c r="D2" s="8">
-        <v>1</v>
-      </c>
-      <c r="E2" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Higher</t>
-        </is>
-      </c>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="9">
-        <v>47.2</v>
-      </c>
-      <c r="I2" s="9">
-        <v>50.6</v>
-      </c>
-      <c r="J2" s="9">
-        <v>336</v>
-      </c>
-      <c r="K2" s="9">
-        <v>351.4</v>
+          <t xml:space="preserve">Plant shut down July 13-17 for a utility transformer replacement at the point of interconnection.</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Revenue</t>
+          <t xml:space="preserve">Operating income ($MM)</t>
         </is>
       </c>
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">$</t>
+          <t xml:space="preserve">Jan</t>
         </is>
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">MM</t>
-        </is>
-      </c>
-      <c r="D3" s="8">
-        <v>2</v>
-      </c>
-      <c r="E3" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Higher</t>
-        </is>
-      </c>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="10">
-        <v>3.92</v>
-      </c>
-      <c r="I3" s="10">
-        <v>3.85</v>
-      </c>
-      <c r="J3" s="10">
-        <v>24.71</v>
-      </c>
-      <c r="K3" s="10">
-        <v>25.3</v>
+          <t xml:space="preserve">Annual property insurance premium expensed in January.</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">O&amp;M expense</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">$</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MM</t>
-        </is>
-      </c>
-      <c r="D4" s="8">
-        <v>2</v>
-      </c>
-      <c r="E4" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Lower</t>
-        </is>
-      </c>
-      <c r="F4" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Abs</t>
-        </is>
-      </c>
-      <c r="G4" s="8"/>
-      <c r="H4" s="10">
-        <v>0.86</v>
-      </c>
-      <c r="I4" s="10">
-        <v>0.74</v>
-      </c>
-      <c r="J4" s="10">
-        <v>6.12</v>
-      </c>
-      <c r="K4" s="10">
-        <v>6.4</v>
-      </c>
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Operating income</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">$</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MM</t>
-        </is>
-      </c>
-      <c r="D5" s="8">
-        <v>2</v>
-      </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Higher</t>
-        </is>
-      </c>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Y</t>
-        </is>
-      </c>
-      <c r="H5" s="10">
-        <v>2.07</v>
-      </c>
-      <c r="I5" s="10">
-        <v>2.31</v>
-      </c>
-      <c r="J5" s="10">
-        <v>10.48</v>
-      </c>
-      <c r="K5" s="10">
-        <v>11.62</v>
-      </c>
+      <c r="A5" s="8"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="8"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
     </row>
   </sheetData>
-  <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E200">
-      <formula1>"Higher,Lower"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F200">
-      <formula1>"%,Abs,Pts"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G200">
-      <formula1>"Y,N"</formula1>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B200">
+      <formula1>"Jan,Feb,Mar,Apr,May,Jun,Jul,Aug,Sep,Oct,Nov,Dec"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1331,6 +1231,329 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
+    <col min="1" max="1" width="26" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="8" customWidth="1"/>
+    <col min="6" max="6" width="8" customWidth="1"/>
+    <col min="7" max="7" width="10" customWidth="1"/>
+    <col min="8" max="8" width="13" customWidth="1"/>
+    <col min="9" max="9" width="13" customWidth="1"/>
+    <col min="10" max="10" width="7" customWidth="1"/>
+    <col min="11" max="11" width="14" customWidth="1"/>
+    <col min="12" max="12" width="15" customWidth="1"/>
+    <col min="13" max="13" width="13" customWidth="1"/>
+    <col min="14" max="14" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Metric</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">From Chart</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">From Component</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YTD Method</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prefix</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Suffix</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Decimals</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Better When</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Variance As</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bold</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Month Actual</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Month EV Case</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YTD Actual</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YTD EV Case</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Generation</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Generation (GWh)</t>
+        </is>
+      </c>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sum</t>
+        </is>
+      </c>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> GWh</t>
+        </is>
+      </c>
+      <c r="G2" s="8">
+        <v>1</v>
+      </c>
+      <c r="H2" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Higher</t>
+        </is>
+      </c>
+      <c r="I2" s="8"/>
+      <c r="J2" s="8"/>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(from Charts)</t>
+        </is>
+      </c>
+      <c r="L2" s="9">
+        <v>50.6</v>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(from Charts)</t>
+        </is>
+      </c>
+      <c r="N2" s="9">
+        <v>351.4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Revenue</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Revenue ($MM)</t>
+        </is>
+      </c>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sum</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$</t>
+        </is>
+      </c>
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MM</t>
+        </is>
+      </c>
+      <c r="G3" s="8">
+        <v>2</v>
+      </c>
+      <c r="H3" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Higher</t>
+        </is>
+      </c>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(from Charts)</t>
+        </is>
+      </c>
+      <c r="L3" s="10">
+        <v>3.85</v>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(from Charts)</t>
+        </is>
+      </c>
+      <c r="N3" s="10">
+        <v>25.3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">O&amp;M expense</t>
+        </is>
+      </c>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sum</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MM</t>
+        </is>
+      </c>
+      <c r="G4" s="8">
+        <v>2</v>
+      </c>
+      <c r="H4" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lower</t>
+        </is>
+      </c>
+      <c r="I4" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Abs</t>
+        </is>
+      </c>
+      <c r="J4" s="8"/>
+      <c r="K4" s="10">
+        <v>0.86</v>
+      </c>
+      <c r="L4" s="10">
+        <v>0.74</v>
+      </c>
+      <c r="M4" s="10">
+        <v>6.12</v>
+      </c>
+      <c r="N4" s="10">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Operating income</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Operating income ($MM)</t>
+        </is>
+      </c>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sum</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MM</t>
+        </is>
+      </c>
+      <c r="G5" s="8">
+        <v>2</v>
+      </c>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Higher</t>
+        </is>
+      </c>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(from Charts)</t>
+        </is>
+      </c>
+      <c r="L5" s="10">
+        <v>2.31</v>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(from Charts)</t>
+        </is>
+      </c>
+      <c r="N5" s="10">
+        <v>11.62</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="4">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D200">
+      <formula1>"Sum,Average"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H200">
+      <formula1>"Higher,Lower"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I200">
+      <formula1>"%,Abs,Pts"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J200">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="2" width="90" customWidth="1"/>
   </cols>
@@ -1350,12 +1573,12 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Inverter block 3</t>
+          <t xml:space="preserve">Interconnection</t>
         </is>
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Two central inverters offline August 4-9 for warranty replacement of power modules.</t>
+          <t xml:space="preserve">Utility replaced the POI transformer July 13-17; the plant was offline for the full outage.</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1611,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>

--- a/dashboard-builder/Bluefield-Example-Inputs.xlsx
+++ b/dashboard-builder/Bluefield-Example-Inputs.xlsx
@@ -516,12 +516,12 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">This year</t>
+          <t xml:space="preserve">Both years</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Which bars get value labels: This year / Both years / None.</t>
+          <t xml:space="preserve">Which bars get value labels: Both years / This year / None.</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       <formula1>"Jan,Feb,Mar,Apr,May,Jun,Jul,Aug,Sep,Oct,Nov,Dec"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B10">
-      <formula1>"This year,Both years,None"</formula1>
+      <formula1>"Both years,This year,None"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B11">
       <formula1>"Auto,1,2,3"</formula1>

--- a/dashboard-builder/Bluefield-Example-Inputs.xlsx
+++ b/dashboard-builder/Bluefield-Example-Inputs.xlsx
@@ -12,7 +12,12 @@
     <sheet name="Table" sheetId="5" r:id="rId5"/>
     <sheet name="Commentary" sheetId="6" r:id="rId6"/>
     <sheet name="Side Table" sheetId="7" r:id="rId7"/>
+    <sheet name="Lists" sheetId="8" state="hidden" r:id="rId8"/>
   </sheets>
+  <definedNames>
+    <definedName name="ChartNames">OFFSET(Lists!$A$2,0,0,MAX(1,COUNTIF(Lists!$A$2:$A$101,"?*")),1)</definedName>
+  </definedNames>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -256,7 +261,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Footnotes  -  explain a month on a chart.  Leave "Chart" blank to mark that month on every chart.</t>
+          <t xml:space="preserve">Footnotes  -  explain a month on a chart.  Pick the chart from the dropdown, or leave "Chart" blank to mark that month on every chart.</t>
         </is>
       </c>
     </row>
@@ -277,7 +282,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">               Put a chart name in "From Chart" to fill Month Actual and YTD Actual from the Charts tab automatically</t>
+          <t xml:space="preserve">               Pick a chart in "From Chart" (dropdown) to fill Month Actual and YTD Actual from the Charts tab automatically</t>
         </is>
       </c>
     </row>
@@ -340,6 +345,13 @@
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-  The Chart dropdowns list the names on the Charts tab automatically (from a hidden "Lists" tab).  Add a chart there and it appears in the dropdowns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t xml:space="preserve">-  Your data never leaves your computer: the builder page reads the file locally in the browser.</t>
         </is>
@@ -1218,7 +1230,10 @@
       <c r="C6" s="8"/>
     </row>
   </sheetData>
-  <dataValidations count="1">
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A200">
+      <formula1>ChartNames</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B200">
       <formula1>"Jan,Feb,Mar,Apr,May,Jun,Jul,Aug,Sep,Oct,Nov,Dec"</formula1>
     </dataValidation>
@@ -1532,7 +1547,10 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="4">
+  <dataValidations count="5">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B200">
+      <formula1>ChartNames</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D200">
       <formula1>"Sum,Average"</formula1>
     </dataValidation>
@@ -1637,4 +1655,623 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="30" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chart names</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A1,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A2,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A3,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A4,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A5,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A6,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A7,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A8,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A9,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A10,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A11,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A12,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A13,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A14,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A15,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A16,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A17,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A18,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A19,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A20,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A21,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A22,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A23,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A24,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A25,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A26,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A27,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A28,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A29,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A30,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A31,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A32,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A33,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A34,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A35,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A36,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A37,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A38,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A39,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A40,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A41,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A42,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A43,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A44,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A45,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A46,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A47,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A48,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A49,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A50,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A51,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A52,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A53,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A54,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A55,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A56,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A57,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A58,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A59,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A60,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A61,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A62,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A63,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A64,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A65,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A66,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A67,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A68,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A69,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A70,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A71,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A72,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A73,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A74,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A75,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A76,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A77,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A78,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A79,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A80,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A81,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A82,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A83,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A84,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A85,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A86,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A87,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A88,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A89,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A90,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A91,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A92,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A93,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A94,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A95,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A96,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A97,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A98,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A99,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A100,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/dashboard-builder/Bluefield-Example-Inputs.xlsx
+++ b/dashboard-builder/Bluefield-Example-Inputs.xlsx
@@ -12,7 +12,9 @@
     <sheet name="Table" sheetId="5" r:id="rId5"/>
     <sheet name="Commentary" sheetId="6" r:id="rId6"/>
     <sheet name="Side Table" sheetId="7" r:id="rId7"/>
-    <sheet name="Lists" sheetId="8" state="hidden" r:id="rId8"/>
+    <sheet name="Debt Service" sheetId="8" r:id="rId8"/>
+    <sheet name="DSCR Notes" sheetId="9" r:id="rId9"/>
+    <sheet name="Lists" sheetId="10" state="hidden" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="ChartNames">OFFSET(Lists!$A$2,0,0,MAX(1,COUNTIF(Lists!$A$2:$A$101,"?*")),1)</definedName>
@@ -321,40 +323,687 @@
         </is>
       </c>
     </row>
-    <row r="25"/>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Debt Service  -  quarterly cash flow for page 2.  One column per quarter, oldest on the left.  Role: Revenue, Expense or Debt service.</t>
+        </is>
+      </c>
+    </row>
     <row r="26">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tips</t>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">               Enter expenses and debt service as positive numbers.  CFADS = Revenue - Expenses.  DSCR = CFADS / Debt service.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">-  Do not rename the tabs or the column headers in row 1.  You can add, delete or reorder rows freely.</t>
+          <t xml:space="preserve">               LTM DSCR = last 4 quarters of CFADS / last 4 quarters of debt service.  Add any expense or debt service rows you need.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t xml:space="preserve">DSCR Notes  -  optional Heading + Text pairs shown beside the cash flow table on page 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tips</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-  Do not rename the tabs or the column headers in row 1.  You can add, delete or reorder rows freely.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t xml:space="preserve">-  Copy this workbook for each asset (one workbook = one dashboard).</t>
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-  The Chart dropdowns list the names on the Charts tab automatically (from a hidden "Lists" tab).  Add a chart there and it appears in the dropdowns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-  Your data never leaves your computer: the builder page reads the file locally in the browser.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="30" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chart names</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A1,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A2,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A3,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A4,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A5,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A6,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A7,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A8,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A9,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A10,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A11,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A12,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A13,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A14,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A15,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A16,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A17,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A18,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A19,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A20,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A21,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A22,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A23,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A24,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A25,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A26,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A27,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-  The Chart dropdowns list the names on the Charts tab automatically (from a hidden "Lists" tab).  Add a chart there and it appears in the dropdowns.</t>
-        </is>
+      <c r="A29" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A28,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-  Your data never leaves your computer: the builder page reads the file locally in the browser.</t>
-        </is>
+      <c r="A30" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A29,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A30,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A31,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A32,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A33,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A34,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A35,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A36,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A37,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A38,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A39,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A40,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A41,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A42,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A43,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A44,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A45,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A46,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A47,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A48,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A49,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A50,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A51,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A52,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A53,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A54,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A55,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A56,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A57,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A58,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A59,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A60,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A61,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A62,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A63,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A64,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A65,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A66,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A67,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A68,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A69,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A70,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A71,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A72,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A73,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A74,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A75,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A76,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A77,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A78,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A79,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A80,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A81,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A82,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A83,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A84,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A85,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A86,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A87,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A88,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A89,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A90,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A91,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A92,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A93,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A94,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A95,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A96,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A97,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A98,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A99,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A100,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -748,8 +1397,119 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include DSCR page</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Auto</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Auto = add page 2 (Debt Service Coverage) when the Debt Service tab has data.  Yes / No to force it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DSCR page title</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Debt Service Coverage - LTM Basis</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Header above the DSCR charts on page 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quarters shown</t>
+        </is>
+      </c>
+      <c r="B26" s="8">
+        <v>4</v>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">How many of the most recent quarters page 2 shows (1-8).  Enter 3 extra older quarters to show an LTM DSCR for every quarter shown.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lock-up DSCR</t>
+        </is>
+      </c>
+      <c r="B27" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Distribution lock-up covenant, e.g. 1.20.  Drawn as a reference line; leave blank for none.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default DSCR</t>
+        </is>
+      </c>
+      <c r="B28" s="8">
+        <v>1.1</v>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default covenant, e.g. 1.10.  Drawn as a reference line; leave blank for none.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cash flow units</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$MM</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Units label for page 2, e.g. $MM or $000s.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cash flow decimals</t>
+        </is>
+      </c>
+      <c r="B30" s="8">
+        <v>2</v>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Decimals in the page 2 cash flow table.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <dataValidations count="6">
+  <dataValidations count="7">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B8">
       <formula1>"Jan,Feb,Mar,Apr,May,Jun,Jul,Aug,Sep,Oct,Nov,Dec"</formula1>
     </dataValidation>
@@ -767,6 +1527,9 @@
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B23">
       <formula1>"Letter,A4"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B24">
+      <formula1>"Auto,Yes,No"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1661,614 +2424,336 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="1" max="1" width="26" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="11" customWidth="1"/>
+    <col min="4" max="4" width="11" customWidth="1"/>
+    <col min="5" max="5" width="11" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="11" customWidth="1"/>
+    <col min="9" max="9" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Chart names</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Line item</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Role</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q4 2024</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q1 2025</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q2 2025</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q3 2025</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q4 2025</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q1 2026</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q2 2026</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A1,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Revenue</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Revenue</t>
+        </is>
+      </c>
+      <c r="C2" s="10">
+        <v>5.31</v>
+      </c>
+      <c r="D2" s="10">
+        <v>5.62</v>
+      </c>
+      <c r="E2" s="10">
+        <v>10.04</v>
+      </c>
+      <c r="F2" s="10">
+        <v>10.52</v>
+      </c>
+      <c r="G2" s="10">
+        <v>5.93</v>
+      </c>
+      <c r="H2" s="10">
+        <v>6.08</v>
+      </c>
+      <c r="I2" s="10">
+        <v>10.61</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A2,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">O&amp;M</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Expense</t>
+        </is>
+      </c>
+      <c r="C3" s="10">
+        <v>1.92</v>
+      </c>
+      <c r="D3" s="10">
+        <v>2.01</v>
+      </c>
+      <c r="E3" s="10">
+        <v>2.08</v>
+      </c>
+      <c r="F3" s="10">
+        <v>2.17</v>
+      </c>
+      <c r="G3" s="10">
+        <v>2.03</v>
+      </c>
+      <c r="H3" s="10">
+        <v>2.11</v>
+      </c>
+      <c r="I3" s="10">
+        <v>2.19</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A3,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Property taxes</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Expense</t>
+        </is>
+      </c>
+      <c r="C4" s="10">
+        <v>0.4</v>
+      </c>
+      <c r="D4" s="10">
+        <v>0.4</v>
+      </c>
+      <c r="E4" s="10">
+        <v>0.4</v>
+      </c>
+      <c r="F4" s="10">
+        <v>0.4</v>
+      </c>
+      <c r="G4" s="10">
+        <v>0.42</v>
+      </c>
+      <c r="H4" s="10">
+        <v>0.45</v>
+      </c>
+      <c r="I4" s="10">
+        <v>0.45</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A4,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Other taxes</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Expense</t>
+        </is>
+      </c>
+      <c r="C5" s="10">
+        <v>0.11</v>
+      </c>
+      <c r="D5" s="10">
+        <v>0.09</v>
+      </c>
+      <c r="E5" s="10">
+        <v>0.18</v>
+      </c>
+      <c r="F5" s="10">
+        <v>0.21</v>
+      </c>
+      <c r="G5" s="10">
+        <v>0.1</v>
+      </c>
+      <c r="H5" s="10">
+        <v>0.08</v>
+      </c>
+      <c r="I5" s="10">
+        <v>0.19</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A5,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Principal</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Debt service</t>
+        </is>
+      </c>
+      <c r="C6" s="10">
+        <v>2.4</v>
+      </c>
+      <c r="D6" s="10">
+        <v>2.42</v>
+      </c>
+      <c r="E6" s="10">
+        <v>2.48</v>
+      </c>
+      <c r="F6" s="10">
+        <v>2.51</v>
+      </c>
+      <c r="G6" s="10">
+        <v>2.57</v>
+      </c>
+      <c r="H6" s="10">
+        <v>2.62</v>
+      </c>
+      <c r="I6" s="10">
+        <v>2.68</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A6,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Interest</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Debt service</t>
+        </is>
+      </c>
+      <c r="C7" s="10">
+        <v>1.91</v>
+      </c>
+      <c r="D7" s="10">
+        <v>1.86</v>
+      </c>
+      <c r="E7" s="10">
+        <v>1.81</v>
+      </c>
+      <c r="F7" s="10">
+        <v>1.76</v>
+      </c>
+      <c r="G7" s="10">
+        <v>1.7</v>
+      </c>
+      <c r="H7" s="10">
+        <v>1.65</v>
+      </c>
+      <c r="I7" s="10">
+        <v>1.6</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A7,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
+      <c r="A8" s="8"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="10"/>
+      <c r="H8" s="10"/>
+      <c r="I8" s="10"/>
     </row>
     <row r="9">
-      <c r="A9" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A8,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A9,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A10,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A11,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A12,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A13,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A14,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A15,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A16,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A17,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A18,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A19,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A20,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A21,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A22,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A23,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A24,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A25,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A26,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A27,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A28,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A29,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A30,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A31,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A32,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A33,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A34,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A35,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A36,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A37,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A38,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A39,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A40,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A41,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A42,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A43,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A44,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A45,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A46,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A47,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A48,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A49,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A50,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A51,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A52,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A53,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A54,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A55,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A56,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A57,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A58,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A59,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A60,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A61,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A62,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A63,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A64,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A65,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A66,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A67,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A68,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A69,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A70,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A71,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A72,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A73,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A74,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A75,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A76,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A77,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A78,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A79,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A80,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A81,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A82,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A83,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A84,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A85,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A86,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A87,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A88,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A89,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A90,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A91,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A92,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A93,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A94,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A95,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A96,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A97,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A98,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A99,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="str">
-        <f>IFERROR(INDEX(Charts!$A$2:$A$500,MATCH(0,INDEX(COUNTIF($A$1:A100,Charts!$A$2:$A$500)+(Charts!$A$2:$A$500=""),0),0)),"")</f>
-        <v/>
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="10"/>
+      <c r="I9" s="10"/>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B100">
+      <formula1>"Revenue,Expense,Debt service"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="2" max="2" width="90" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heading</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Text</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Seasonality</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q1 and Q4 coverage falls below 1.0x on a stand-alone basis every year; the covenants test on an LTM basis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Next test</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q3 2026 test at September 30, 2026.  Distributions require 1.20x LTM.</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/dashboard-builder/Bluefield-Example-Inputs.xlsx
+++ b/dashboard-builder/Bluefield-Example-Inputs.xlsx
@@ -13,8 +13,9 @@
     <sheet name="Commentary" sheetId="6" r:id="rId6"/>
     <sheet name="Side Table" sheetId="7" r:id="rId7"/>
     <sheet name="Debt Service" sheetId="8" r:id="rId8"/>
-    <sheet name="DSCR Notes" sheetId="9" r:id="rId9"/>
-    <sheet name="Lists" sheetId="10" state="hidden" r:id="rId10"/>
+    <sheet name="Reserves" sheetId="9" r:id="rId9"/>
+    <sheet name="DSCR Notes" sheetId="10" r:id="rId10"/>
+    <sheet name="Lists" sheetId="11" state="hidden" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="ChartNames">OFFSET(Lists!$A$2,0,0,MAX(1,COUNTIF(Lists!$A$2:$A$101,"?*")),1)</definedName>
@@ -347,41 +348,55 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">DSCR Notes  -  optional Heading + Text pairs shown beside the cash flow table on page 2.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29"/>
+          <t xml:space="preserve">Reserves  -  one row per reserve account (DSR, O&amp;M reserve, ...): Required balance and Balance available.  Shown on page 2 below the DSCR chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">               with the % funded; anything under 100% is flagged.</t>
+        </is>
+      </c>
+    </row>
     <row r="30">
-      <c r="A30" s="6" t="inlineStr">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DSCR Notes  -  optional Heading + Text pairs shown on page 2 below the reserves.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Tips</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-  Do not rename the tabs or the column headers in row 1.  You can add, delete or reorder rows freely.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-  Copy this workbook for each asset (one workbook = one dashboard).</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">-  The Chart dropdowns list the names on the Charts tab automatically (from a hidden "Lists" tab).  Add a chart there and it appears in the dropdowns.</t>
+          <t xml:space="preserve">-  Do not rename the tabs or the column headers in row 1.  You can add, delete or reorder rows freely.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-  Copy this workbook for each asset (one workbook = one dashboard).</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-  The Chart dropdowns list the names on the Charts tab automatically (from a hidden "Lists" tab).  Add a chart there and it appears in the dropdowns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
         <is>
           <t xml:space="preserve">-  Your data never leaves your computer: the builder page reads the file locally in the browser.</t>
         </is>
@@ -393,6 +408,55 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="2" max="2" width="90" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heading</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Text</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Seasonality</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q1 and Q4 coverage falls below 1.0x on a stand-alone basis every year; the covenants test on an LTM basis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Next test</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q3 2026 test at September 30, 2026.  Distributions require 1.20x LTM.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -1449,7 +1513,7 @@
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lock-up DSCR</t>
+          <t xml:space="preserve">Distribution lock-up DSCR</t>
         </is>
       </c>
       <c r="B27" s="8">
@@ -1457,7 +1521,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Distribution lock-up covenant, e.g. 1.20.  Drawn as a reference line; leave blank for none.</t>
+          <t xml:space="preserve">Distribution lock-up covenant, e.g. 1.20.  Drawn as a reference line.  Leave blank and it does not appear anywhere.</t>
         </is>
       </c>
     </row>
@@ -1472,37 +1536,54 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Default covenant, e.g. 1.10.  Drawn as a reference line; leave blank for none.</t>
+          <t xml:space="preserve">Default covenant, e.g. 1.10.  Drawn as a reference line.  Leave blank and it does not appear anywhere.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cash flow units</t>
+          <t xml:space="preserve">Reserves title</t>
         </is>
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">$MM</t>
+          <t xml:space="preserve">DSR and O&amp;M Reserves</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Units label for page 2, e.g. $MM or $000s.</t>
+          <t xml:space="preserve">Header of the reserves box on page 2 (below the DSCR chart).</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
+          <t xml:space="preserve">Cash flow units</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$MM</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Units label for page 2, e.g. $MM or $000s.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
           <t xml:space="preserve">Cash flow decimals</t>
         </is>
       </c>
-      <c r="B30" s="8">
+      <c r="B31" s="8">
         <v>2</v>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Decimals in the page 2 cash flow table.</t>
         </is>
@@ -2716,45 +2797,63 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="2" width="90" customWidth="1"/>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heading</t>
+          <t xml:space="preserve">Reserve</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Text</t>
+          <t xml:space="preserve">Required</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Balance available</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seasonality</t>
-        </is>
-      </c>
-      <c r="B2" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Q1 and Q4 coverage falls below 1.0x on a stand-alone basis every year; the covenants test on an LTM basis.</t>
-        </is>
+          <t xml:space="preserve">Debt service reserve</t>
+        </is>
+      </c>
+      <c r="B2" s="10">
+        <v>8.55</v>
+      </c>
+      <c r="C2" s="10">
+        <v>8.62</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Next test</t>
-        </is>
-      </c>
-      <c r="B3" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Q3 2026 test at September 30, 2026.  Distributions require 1.20x LTM.</t>
-        </is>
-      </c>
+          <t xml:space="preserve">O&amp;M reserve</t>
+        </is>
+      </c>
+      <c r="B3" s="10">
+        <v>2.1</v>
+      </c>
+      <c r="C3" s="10">
+        <v>1.85</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="8"/>
+      <c r="B5" s="10"/>
+      <c r="C5" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/dashboard-builder/Bluefield-Example-Inputs.xlsx
+++ b/dashboard-builder/Bluefield-Example-Inputs.xlsx
@@ -19,6 +19,8 @@
   </sheets>
   <definedNames>
     <definedName name="ChartNames">OFFSET(Lists!$A$2,0,0,MAX(1,COUNTIF(Lists!$A$2:$A$101,"?*")),1)</definedName>
+    <definedName name="CurYear">Settings!$B$6</definedName>
+    <definedName name="CurMonthNum">IF(ISNUMBER(Settings!$B$8),Settings!$B$8,MATCH(LEFT(Settings!$B$8,3),{"Jan","Feb","Mar","Apr","May","Jun","Jul","Aug","Sep","Oct","Nov","Dec"},0))</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -131,7 +133,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -154,6 +156,9 @@
     <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -285,118 +290,132 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">               Pick a chart in "From Chart" (dropdown) to fill Month Actual and YTD Actual from the Charts tab automatically</t>
+          <t xml:space="preserve">               Month Actual and YTD Actual (black cells) are formulas: rows with a "From Chart" sum that chart on the Charts tab for the</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">               (add a "From Component" to use just one component, e.g. Contracted).  Leave "From Chart" blank to type the actuals yourself.</t>
+          <t xml:space="preserve">               Current year, for the Current month and Jan through it (add a "From Component" to use one component, e.g. Contracted).</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">               "YTD Method": Sum (default) adds the months up; Average averages them (use for percentages like capacity factor).</t>
+          <t xml:space="preserve">               O&amp;M expense defaults to Revenue - Operating income.  Type a number over any formula to override it; the PDF uses the cell value.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">               Month EV Case and YTD EV Case are always typed in.</t>
+          <t xml:space="preserve">               Rows with no "From Chart" and no formula: type the actuals yourself.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commentary  -  Heading + Text pairs for the bottom-right box.</t>
+          <t xml:space="preserve">               "YTD Method": Sum (default) adds the months up; Average averages them (use for percentages like capacity factor).</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Side Table  -  a free-form grid for the bottom-right box.  Row 1 = column headers.  Values print exactly as they appear in Excel.</t>
+          <t xml:space="preserve">               Month EV Case and YTD EV Case are always typed in.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Debt Service  -  quarterly cash flow for page 2.  One column per quarter, oldest on the left.  Role: Revenue, Expense or Debt service.</t>
+          <t xml:space="preserve">Commentary  -  Heading + Text pairs for the bottom-right box.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">               Enter expenses and debt service as positive numbers.  CFADS = Revenue - Expenses.  DSCR = CFADS / Debt service.</t>
+          <t xml:space="preserve">Side Table  -  a free-form grid for the bottom-right box.  Row 1 = column headers.  Values print exactly as they appear in Excel.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">               LTM DSCR = last 4 quarters of CFADS / last 4 quarters of debt service.  Add any expense or debt service rows you need.</t>
+          <t xml:space="preserve">Debt Service  -  quarterly cash flow for page 2.  One column per quarter, oldest on the left.  Role: Revenue, Expense or Debt service.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reserves  -  one row per reserve account (DSR, O&amp;M reserve, ...): Required balance and Balance available.  Shown on page 2 below the DSCR chart</t>
+          <t xml:space="preserve">               Enter expenses and debt service as positive numbers.  CFADS = Revenue - Expenses.  DSCR = CFADS / Debt service.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">               with the % funded; anything under 100% is flagged.</t>
+          <t xml:space="preserve">               LTM DSCR = last 4 quarters of CFADS / last 4 quarters of debt service.  Add any expense or debt service rows you need.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t xml:space="preserve">Reserves  -  one row per reserve account (DSR, O&amp;M reserve, ...): Required balance and Balance available.  Shown on page 2 below the DSCR chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">               with the % funded; anything under 100% is flagged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t xml:space="preserve">DSCR Notes  -  optional Heading + Text pairs shown on page 2 below the reserves.</t>
         </is>
       </c>
     </row>
-    <row r="31"/>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
+    <row r="33"/>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Tips</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-  Do not rename the tabs or the column headers in row 1.  You can add, delete or reorder rows freely.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-  Copy this workbook for each asset (one workbook = one dashboard).</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">-  The Chart dropdowns list the names on the Charts tab automatically (from a hidden "Lists" tab).  Add a chart there and it appears in the dropdowns.</t>
+          <t xml:space="preserve">-  Do not rename the tabs or the column headers in row 1.  You can add, delete or reorder rows freely.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-  Copy this workbook for each asset (one workbook = one dashboard).</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-  The Chart dropdowns list the names on the Charts tab automatically (from a hidden "Lists" tab).  Add a chart there and it appears in the dropdowns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t xml:space="preserve">-  Your data never leaves your computer: the builder page reads the file locally in the browser.</t>
         </is>
@@ -2211,18 +2230,16 @@
       </c>
       <c r="I2" s="8"/>
       <c r="J2" s="8"/>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(from Charts)</t>
-        </is>
+      <c r="K2" s="13">
+        <f>IF($C2="",SUMIFS(INDEX(Charts!$E$2:$P$500,0,CurMonthNum),Charts!$A$2:$A$500,$B2,Charts!$C$2:$C$500,CurYear),SUMIFS(INDEX(Charts!$E$2:$P$500,0,CurMonthNum),Charts!$A$2:$A$500,$B2,Charts!$C$2:$C$500,CurYear,Charts!$B$2:$B$500,$C2))</f>
+        <v>47.2</v>
       </c>
       <c r="L2" s="9">
         <v>50.6</v>
       </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(from Charts)</t>
-        </is>
+      <c r="M2" s="13">
+        <f>SUMPRODUCT((Charts!$A$2:$A$500=$B2)*(Charts!$C$2:$C$500=CurYear)*((($C2="")+(Charts!$B$2:$B$500=$C2))&gt;0)*(COLUMN(Charts!$E$1:$P$1)-COLUMN(Charts!$E$1)&lt;CurMonthNum),Charts!$E$2:$P$500)/IF($D2="Average",CurMonthNum,1)</f>
+        <v>326</v>
       </c>
       <c r="N2" s="9">
         <v>351.4</v>
@@ -2265,18 +2282,16 @@
       </c>
       <c r="I3" s="8"/>
       <c r="J3" s="8"/>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(from Charts)</t>
-        </is>
+      <c r="K3" s="14">
+        <f>IF($C3="",SUMIFS(INDEX(Charts!$E$2:$P$500,0,CurMonthNum),Charts!$A$2:$A$500,$B3,Charts!$C$2:$C$500,CurYear),SUMIFS(INDEX(Charts!$E$2:$P$500,0,CurMonthNum),Charts!$A$2:$A$500,$B3,Charts!$C$2:$C$500,CurYear,Charts!$B$2:$B$500,$C3))</f>
+        <v>3.92</v>
       </c>
       <c r="L3" s="10">
         <v>3.85</v>
       </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(from Charts)</t>
-        </is>
+      <c r="M3" s="14">
+        <f>SUMPRODUCT((Charts!$A$2:$A$500=$B3)*(Charts!$C$2:$C$500=CurYear)*((($C3="")+(Charts!$B$2:$B$500=$C3))&gt;0)*(COLUMN(Charts!$E$1:$P$1)-COLUMN(Charts!$E$1)&lt;CurMonthNum),Charts!$E$2:$P$500)/IF($D3="Average",CurMonthNum,1)</f>
+        <v>23.97</v>
       </c>
       <c r="N3" s="10">
         <v>25.3</v>
@@ -2319,17 +2334,19 @@
         </is>
       </c>
       <c r="J4" s="8"/>
-      <c r="K4" s="10">
-        <v>0.86</v>
+      <c r="K4" s="14">
+        <f>K3-K5</f>
+        <v>1.85</v>
       </c>
       <c r="L4" s="10">
-        <v>0.74</v>
-      </c>
-      <c r="M4" s="10">
-        <v>6.12</v>
+        <v>1.54</v>
+      </c>
+      <c r="M4" s="14">
+        <f>M3-M5</f>
+        <v>14.38</v>
       </c>
       <c r="N4" s="10">
-        <v>6.4</v>
+        <v>13.68</v>
       </c>
     </row>
     <row r="5">
@@ -2373,18 +2390,16 @@
           <t xml:space="preserve">Y</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(from Charts)</t>
-        </is>
+      <c r="K5" s="14">
+        <f>IF($C5="",SUMIFS(INDEX(Charts!$E$2:$P$500,0,CurMonthNum),Charts!$A$2:$A$500,$B5,Charts!$C$2:$C$500,CurYear),SUMIFS(INDEX(Charts!$E$2:$P$500,0,CurMonthNum),Charts!$A$2:$A$500,$B5,Charts!$C$2:$C$500,CurYear,Charts!$B$2:$B$500,$C5))</f>
+        <v>2.07</v>
       </c>
       <c r="L5" s="10">
         <v>2.31</v>
       </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(from Charts)</t>
-        </is>
+      <c r="M5" s="14">
+        <f>SUMPRODUCT((Charts!$A$2:$A$500=$B5)*(Charts!$C$2:$C$500=CurYear)*((($C5="")+(Charts!$B$2:$B$500=$C5))&gt;0)*(COLUMN(Charts!$E$1:$P$1)-COLUMN(Charts!$E$1)&lt;CurMonthNum),Charts!$E$2:$P$500)/IF($D5="Average",CurMonthNum,1)</f>
+        <v>9.59</v>
       </c>
       <c r="N5" s="10">
         <v>11.62</v>

--- a/dashboard-builder/Bluefield-Example-Inputs.xlsx
+++ b/dashboard-builder/Bluefield-Example-Inputs.xlsx
@@ -318,104 +318,118 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">               "YTD Method": Sum (default) adds the months up; Average averages them (use for percentages like capacity factor).</t>
+          <t xml:space="preserve">               "EV Basis": if the EV Case values were pro-rated from quarterly, semi-annual or annual figures, pick that here.  The EV Case</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">               Month EV Case and YTD EV Case are always typed in.</t>
+          <t xml:space="preserve">               values get a small letter (a, b, ...) and a footnote under the table explains it.  Monthly (the default) adds nothing.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commentary  -  Heading + Text pairs for the bottom-right box.</t>
+          <t xml:space="preserve">               "YTD Method": Sum (default) adds the months up; Average averages them (use for percentages like capacity factor).</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Side Table  -  a free-form grid for the bottom-right box.  Row 1 = column headers.  Values print exactly as they appear in Excel.</t>
+          <t xml:space="preserve">               Month EV Case and YTD EV Case are always typed in.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Debt Service  -  quarterly cash flow for page 2.  One column per quarter, oldest on the left.  Role: Revenue, Expense or Debt service.</t>
+          <t xml:space="preserve">Commentary  -  Heading + Text pairs for the bottom-right box.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">               Enter expenses and debt service as positive numbers.  CFADS = Revenue - Expenses.  DSCR = CFADS / Debt service.</t>
+          <t xml:space="preserve">Side Table  -  a free-form grid for the bottom-right box.  Row 1 = column headers.  Values print exactly as they appear in Excel.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">               LTM DSCR = last 4 quarters of CFADS / last 4 quarters of debt service.  Add any expense or debt service rows you need.</t>
+          <t xml:space="preserve">Debt Service  -  quarterly cash flow for page 2.  One column per quarter, oldest on the left.  Role: Revenue, Expense or Debt service.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reserves  -  one row per reserve account (DSR, O&amp;M reserve, ...): Required balance and Balance available.  Shown on page 2 below the DSCR chart</t>
+          <t xml:space="preserve">               Enter expenses and debt service as positive numbers.  CFADS = Revenue - Expenses.  DSCR = CFADS / Debt service.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">               with the % funded; anything under 100% is flagged.</t>
+          <t xml:space="preserve">               LTM DSCR = last 4 quarters of CFADS / last 4 quarters of debt service.  Add any expense or debt service rows you need.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t xml:space="preserve">Reserves  -  one row per reserve account (DSR, O&amp;M reserve, ...): Required balance and Balance available.  Shown on page 2 below the DSCR chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">               with the % funded; anything under 100% is flagged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t xml:space="preserve">DSCR Notes  -  optional Heading + Text pairs shown on page 2 below the reserves.</t>
         </is>
       </c>
     </row>
-    <row r="33"/>
-    <row r="34">
-      <c r="A34" s="6" t="inlineStr">
+    <row r="35"/>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Tips</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-  Do not rename the tabs or the column headers in row 1.  You can add, delete or reorder rows freely.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-  Copy this workbook for each asset (one workbook = one dashboard).</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">-  The Chart dropdowns list the names on the Charts tab automatically (from a hidden "Lists" tab).  Add a chart there and it appears in the dropdowns.</t>
+          <t xml:space="preserve">-  Do not rename the tabs or the column headers in row 1.  You can add, delete or reorder rows freely.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-  Copy this workbook for each asset (one workbook = one dashboard).</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-  The Chart dropdowns list the names on the Charts tab automatically (from a hidden "Lists" tab).  Add a chart there and it appears in the dropdowns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t xml:space="preserve">-  Your data never leaves your computer: the builder page reads the file locally in the browser.</t>
         </is>
@@ -1483,126 +1497,139 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Include DSCR page</t>
-        </is>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Auto</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Pro-rated note</t>
+        </is>
+      </c>
+      <c r="B24" s="8"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Auto = add page 2 (Debt Service Coverage) when the Debt Service tab has data.  Yes / No to force it.</t>
+          <t xml:space="preserve">Optional wording for the EV Basis footnote under the table.  Blank = "EV Case pro-rated from quarterly figures on a straight-line monthly basis; it does not reflect seasonality within the quarter."  You can use {basis} (quarterly / semi-annual / annual), {period} (quarter / half-year / year) and {comparison} (the Comparison label).</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">DSCR page title</t>
+          <t xml:space="preserve">Include DSCR page</t>
         </is>
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Debt Service Coverage - LTM Basis</t>
+          <t xml:space="preserve">Auto</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Header above the DSCR charts on page 2.</t>
+          <t xml:space="preserve">Auto = add page 2 (Debt Service Coverage) when the Debt Service tab has data.  Yes / No to force it.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quarters shown</t>
-        </is>
-      </c>
-      <c r="B26" s="8">
-        <v>4</v>
+          <t xml:space="preserve">DSCR page title</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Debt Service Coverage - LTM Basis</t>
+        </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">How many of the most recent quarters page 2 shows (1-8).  Enter 3 extra older quarters to show an LTM DSCR for every quarter shown.</t>
+          <t xml:space="preserve">Header above the DSCR charts on page 2.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Distribution lock-up DSCR</t>
+          <t xml:space="preserve">Quarters shown</t>
         </is>
       </c>
       <c r="B27" s="8">
-        <v>1.2</v>
+        <v>4</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Distribution lock-up covenant, e.g. 1.20.  Drawn as a reference line.  Leave blank and it does not appear anywhere.</t>
+          <t xml:space="preserve">How many of the most recent quarters page 2 shows (1-8).  Enter 3 extra older quarters to show an LTM DSCR for every quarter shown.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Default DSCR</t>
+          <t xml:space="preserve">Distribution lock-up DSCR</t>
         </is>
       </c>
       <c r="B28" s="8">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Default covenant, e.g. 1.10.  Drawn as a reference line.  Leave blank and it does not appear anywhere.</t>
+          <t xml:space="preserve">Distribution lock-up covenant, e.g. 1.20.  Drawn as a reference line.  Leave blank and it does not appear anywhere.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reserves title</t>
-        </is>
-      </c>
-      <c r="B29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DSR and O&amp;M Reserves</t>
-        </is>
+          <t xml:space="preserve">Default DSCR</t>
+        </is>
+      </c>
+      <c r="B29" s="8">
+        <v>1.1</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Header of the reserves box on page 2 (below the DSCR chart).</t>
+          <t xml:space="preserve">Default covenant, e.g. 1.10.  Drawn as a reference line.  Leave blank and it does not appear anywhere.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cash flow units</t>
+          <t xml:space="preserve">Reserves title</t>
         </is>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">$MM</t>
+          <t xml:space="preserve">DSR and O&amp;M Reserves</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Units label for page 2, e.g. $MM or $000s.</t>
+          <t xml:space="preserve">Header of the reserves box on page 2 (below the DSCR chart).</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
+          <t xml:space="preserve">Cash flow units</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$MM</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Units label for page 2, e.g. $MM or $000s.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
           <t xml:space="preserve">Cash flow decimals</t>
         </is>
       </c>
-      <c r="B31" s="8">
+      <c r="B32" s="8">
         <v>2</v>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Decimals in the page 2 cash flow table.</t>
         </is>
@@ -1628,7 +1655,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B23">
       <formula1>"Letter,A4"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B24">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B25">
       <formula1>"Auto,Yes,No"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2123,6 +2150,7 @@
     <col min="12" max="12" width="15" customWidth="1"/>
     <col min="13" max="13" width="13" customWidth="1"/>
     <col min="14" max="14" width="14" customWidth="1"/>
+    <col min="15" max="15" width="22" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2194,6 +2222,11 @@
       <c r="N1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">YTD EV Case</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EV Basis</t>
         </is>
       </c>
     </row>
@@ -2244,6 +2277,11 @@
       <c r="N2" s="9">
         <v>351.4</v>
       </c>
+      <c r="O2" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monthly</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
@@ -2296,6 +2334,11 @@
       <c r="N3" s="10">
         <v>25.3</v>
       </c>
+      <c r="O3" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monthly</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
@@ -2348,6 +2391,11 @@
       <c r="N4" s="10">
         <v>13.68</v>
       </c>
+      <c r="O4" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pro-rated annual</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
@@ -2404,9 +2452,14 @@
       <c r="N5" s="10">
         <v>11.62</v>
       </c>
+      <c r="O5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monthly</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <dataValidations count="5">
+  <dataValidations count="6">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B200">
       <formula1>ChartNames</formula1>
     </dataValidation>
@@ -2421,6 +2474,9 @@
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J200">
       <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O200">
+      <formula1>"Monthly,Pro-rated quarterly,Pro-rated semi-annual,Pro-rated annual"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/dashboard-builder/Bluefield-Example-Inputs.xlsx
+++ b/dashboard-builder/Bluefield-Example-Inputs.xlsx
@@ -28,9 +28,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.00"/>
+    <numFmt numFmtId="166" formatCode="0.00&quot;x&quot;"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -133,7 +134,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -159,6 +160,8 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -367,69 +370,83 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">               Enter expenses and debt service as positive numbers.  CFADS = Revenue - Expenses.  DSCR = CFADS / Debt service.</t>
+          <t xml:space="preserve">               Enter expenses and debt service as positive numbers.  The black "Calculated" rows do the math: Total O&amp;M costs = all Expense</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">               LTM DSCR = last 4 quarters of CFADS / last 4 quarters of debt service.  Add any expense or debt service rows you need.</t>
+          <t xml:space="preserve">               rows; CFADS = Revenue - Total O&amp;M costs; Total debt service costs = all Debt service rows; DSCR = CFADS / debt service;</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reserves  -  one row per reserve account (DSR, O&amp;M reserve, ...): Required balance and Balance available.  Shown on page 2 below the DSCR chart</t>
+          <t xml:space="preserve">               DSCR - LTM = last 4 quarters of CFADS / last 4 quarters of debt service.  To add a line (e.g. LC fees), insert a row</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">               with the % funded; anything under 100% is flagged.</t>
+          <t xml:space="preserve">               anywhere and set its Role; the totals pick it up.  The PDF recalculates from the input rows, so it always matches.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t xml:space="preserve">Reserves  -  one row per reserve account (DSR, O&amp;M reserve, ...): Required balance and Balance available.  Shown on page 2 below the DSCR chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">               with the % funded; anything under 100% is flagged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t xml:space="preserve">DSCR Notes  -  optional Heading + Text pairs shown on page 2 below the reserves.</t>
         </is>
       </c>
     </row>
-    <row r="35"/>
-    <row r="36">
-      <c r="A36" s="6" t="inlineStr">
+    <row r="37"/>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Tips</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-  Do not rename the tabs or the column headers in row 1.  You can add, delete or reorder rows freely.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-  Copy this workbook for each asset (one workbook = one dashboard).</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">-  The Chart dropdowns list the names on the Charts tab automatically (from a hidden "Lists" tab).  Add a chart there and it appears in the dropdowns.</t>
+          <t xml:space="preserve">-  Do not rename the tabs or the column headers in row 1.  You can add, delete or reorder rows freely.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-  Copy this workbook for each asset (one workbook = one dashboard).</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-  The Chart dropdowns list the names on the Charts tab automatically (from a hidden "Lists" tab).  Add a chart there and it appears in the dropdowns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
         <is>
           <t xml:space="preserve">-  Your data never leaves your computer: the builder page reads the file locally in the browser.</t>
         </is>
@@ -2767,97 +2784,277 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Total O&amp;M costs</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Calculated</t>
+        </is>
+      </c>
+      <c r="C6" s="15">
+        <f>SUMIF($B$2:$B$200,"Expense",C$2:C$200)</f>
+        <v>2.43</v>
+      </c>
+      <c r="D6" s="15">
+        <f>SUMIF($B$2:$B$200,"Expense",D$2:D$200)</f>
+        <v>2.5</v>
+      </c>
+      <c r="E6" s="15">
+        <f>SUMIF($B$2:$B$200,"Expense",E$2:E$200)</f>
+        <v>2.66</v>
+      </c>
+      <c r="F6" s="15">
+        <f>SUMIF($B$2:$B$200,"Expense",F$2:F$200)</f>
+        <v>2.78</v>
+      </c>
+      <c r="G6" s="15">
+        <f>SUMIF($B$2:$B$200,"Expense",G$2:G$200)</f>
+        <v>2.55</v>
+      </c>
+      <c r="H6" s="15">
+        <f>SUMIF($B$2:$B$200,"Expense",H$2:H$200)</f>
+        <v>2.64</v>
+      </c>
+      <c r="I6" s="15">
+        <f>SUMIF($B$2:$B$200,"Expense",I$2:I$200)</f>
+        <v>2.83</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CFADS</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Calculated</t>
+        </is>
+      </c>
+      <c r="C7" s="15">
+        <f>SUMIF($B$2:$B$200,"Revenue",C$2:C$200)-SUMIF($B$2:$B$200,"Expense",C$2:C$200)</f>
+        <v>2.88</v>
+      </c>
+      <c r="D7" s="15">
+        <f>SUMIF($B$2:$B$200,"Revenue",D$2:D$200)-SUMIF($B$2:$B$200,"Expense",D$2:D$200)</f>
+        <v>3.12</v>
+      </c>
+      <c r="E7" s="15">
+        <f>SUMIF($B$2:$B$200,"Revenue",E$2:E$200)-SUMIF($B$2:$B$200,"Expense",E$2:E$200)</f>
+        <v>7.38</v>
+      </c>
+      <c r="F7" s="15">
+        <f>SUMIF($B$2:$B$200,"Revenue",F$2:F$200)-SUMIF($B$2:$B$200,"Expense",F$2:F$200)</f>
+        <v>7.74</v>
+      </c>
+      <c r="G7" s="15">
+        <f>SUMIF($B$2:$B$200,"Revenue",G$2:G$200)-SUMIF($B$2:$B$200,"Expense",G$2:G$200)</f>
+        <v>3.38</v>
+      </c>
+      <c r="H7" s="15">
+        <f>SUMIF($B$2:$B$200,"Revenue",H$2:H$200)-SUMIF($B$2:$B$200,"Expense",H$2:H$200)</f>
+        <v>3.44</v>
+      </c>
+      <c r="I7" s="15">
+        <f>SUMIF($B$2:$B$200,"Revenue",I$2:I$200)-SUMIF($B$2:$B$200,"Expense",I$2:I$200)</f>
+        <v>7.78</v>
+      </c>
+    </row>
+    <row r="8"/>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Principal</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Debt service</t>
         </is>
       </c>
-      <c r="C6" s="10">
+      <c r="C9" s="10">
         <v>2.4</v>
       </c>
-      <c r="D6" s="10">
+      <c r="D9" s="10">
         <v>2.42</v>
       </c>
-      <c r="E6" s="10">
+      <c r="E9" s="10">
         <v>2.48</v>
       </c>
-      <c r="F6" s="10">
+      <c r="F9" s="10">
         <v>2.51</v>
       </c>
-      <c r="G6" s="10">
+      <c r="G9" s="10">
         <v>2.57</v>
       </c>
-      <c r="H6" s="10">
+      <c r="H9" s="10">
         <v>2.62</v>
       </c>
-      <c r="I6" s="10">
+      <c r="I9" s="10">
         <v>2.68</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Interest</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Debt service</t>
         </is>
       </c>
-      <c r="C7" s="10">
+      <c r="C10" s="10">
         <v>1.91</v>
       </c>
-      <c r="D7" s="10">
+      <c r="D10" s="10">
         <v>1.86</v>
       </c>
-      <c r="E7" s="10">
+      <c r="E10" s="10">
         <v>1.81</v>
       </c>
-      <c r="F7" s="10">
+      <c r="F10" s="10">
         <v>1.76</v>
       </c>
-      <c r="G7" s="10">
+      <c r="G10" s="10">
         <v>1.7</v>
       </c>
-      <c r="H7" s="10">
+      <c r="H10" s="10">
         <v>1.65</v>
       </c>
-      <c r="I7" s="10">
+      <c r="I10" s="10">
         <v>1.6</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="10"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10"/>
-      <c r="I9" s="10"/>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Total debt service costs</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Calculated</t>
+        </is>
+      </c>
+      <c r="C11" s="15">
+        <f>SUMIF($B$2:$B$200,"Debt service",C$2:C$200)</f>
+        <v>4.31</v>
+      </c>
+      <c r="D11" s="15">
+        <f>SUMIF($B$2:$B$200,"Debt service",D$2:D$200)</f>
+        <v>4.28</v>
+      </c>
+      <c r="E11" s="15">
+        <f>SUMIF($B$2:$B$200,"Debt service",E$2:E$200)</f>
+        <v>4.29</v>
+      </c>
+      <c r="F11" s="15">
+        <f>SUMIF($B$2:$B$200,"Debt service",F$2:F$200)</f>
+        <v>4.27</v>
+      </c>
+      <c r="G11" s="15">
+        <f>SUMIF($B$2:$B$200,"Debt service",G$2:G$200)</f>
+        <v>4.27</v>
+      </c>
+      <c r="H11" s="15">
+        <f>SUMIF($B$2:$B$200,"Debt service",H$2:H$200)</f>
+        <v>4.27</v>
+      </c>
+      <c r="I11" s="15">
+        <f>SUMIF($B$2:$B$200,"Debt service",I$2:I$200)</f>
+        <v>4.28</v>
+      </c>
+    </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DSCR - quarter</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Calculated</t>
+        </is>
+      </c>
+      <c r="C13" s="16">
+        <f>IFERROR(C7/C11,"")</f>
+        <v>0.668213</v>
+      </c>
+      <c r="D13" s="16">
+        <f>IFERROR(D7/D11,"")</f>
+        <v>0.728972</v>
+      </c>
+      <c r="E13" s="16">
+        <f>IFERROR(E7/E11,"")</f>
+        <v>1.72028</v>
+      </c>
+      <c r="F13" s="16">
+        <f>IFERROR(F7/F11,"")</f>
+        <v>1.812646</v>
+      </c>
+      <c r="G13" s="16">
+        <f>IFERROR(G7/G11,"")</f>
+        <v>0.791569</v>
+      </c>
+      <c r="H13" s="16">
+        <f>IFERROR(H7/H11,"")</f>
+        <v>0.805621</v>
+      </c>
+      <c r="I13" s="16">
+        <f>IFERROR(I7/I11,"")</f>
+        <v>1.817757</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DSCR - LTM</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Calculated</t>
+        </is>
+      </c>
+      <c r="C14" s="16" t="str">
+        <f>""</f>
+        <v/>
+      </c>
+      <c r="D14" s="16" t="str">
+        <f>""</f>
+        <v/>
+      </c>
+      <c r="E14" s="16" t="str">
+        <f>""</f>
+        <v/>
+      </c>
+      <c r="F14" s="16">
+        <f>IFERROR(SUM(C7:F7)/SUM(C11:F11),"")</f>
+        <v>1.231487</v>
+      </c>
+      <c r="G14" s="16">
+        <f>IFERROR(SUM(D7:G7)/SUM(D11:G11),"")</f>
+        <v>1.263589</v>
+      </c>
+      <c r="H14" s="16">
+        <f>IFERROR(SUM(E7:H7)/SUM(E11:H11),"")</f>
+        <v>1.283041</v>
+      </c>
+      <c r="I14" s="16">
+        <f>IFERROR(SUM(F7:I7)/SUM(F11:I11),"")</f>
+        <v>1.307197</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B100">
-      <formula1>"Revenue,Expense,Debt service"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B200">
+      <formula1>"Revenue,Expense,Debt service,Calculated"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/dashboard-builder/Bluefield-Example-Inputs.xlsx
+++ b/dashboard-builder/Bluefield-Example-Inputs.xlsx
@@ -2684,43 +2684,11 @@
         <v>10.61</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">O&amp;M</t>
-        </is>
-      </c>
-      <c r="B3" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Expense</t>
-        </is>
-      </c>
-      <c r="C3" s="10">
-        <v>1.92</v>
-      </c>
-      <c r="D3" s="10">
-        <v>2.01</v>
-      </c>
-      <c r="E3" s="10">
-        <v>2.08</v>
-      </c>
-      <c r="F3" s="10">
-        <v>2.17</v>
-      </c>
-      <c r="G3" s="10">
-        <v>2.03</v>
-      </c>
-      <c r="H3" s="10">
-        <v>2.11</v>
-      </c>
-      <c r="I3" s="10">
-        <v>2.19</v>
-      </c>
-    </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Property taxes</t>
+          <t xml:space="preserve">O&amp;M</t>
         </is>
       </c>
       <c r="B4" s="8" t="inlineStr">
@@ -2729,325 +2697,358 @@
         </is>
       </c>
       <c r="C4" s="10">
-        <v>0.4</v>
+        <v>1.92</v>
       </c>
       <c r="D4" s="10">
-        <v>0.4</v>
+        <v>2.01</v>
       </c>
       <c r="E4" s="10">
-        <v>0.4</v>
+        <v>2.08</v>
       </c>
       <c r="F4" s="10">
-        <v>0.4</v>
+        <v>2.17</v>
       </c>
       <c r="G4" s="10">
-        <v>0.42</v>
+        <v>2.03</v>
       </c>
       <c r="H4" s="10">
-        <v>0.45</v>
+        <v>2.11</v>
       </c>
       <c r="I4" s="10">
-        <v>0.45</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">Property taxes</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Expense</t>
+        </is>
+      </c>
+      <c r="C5" s="10">
+        <v>0.4</v>
+      </c>
+      <c r="D5" s="10">
+        <v>0.4</v>
+      </c>
+      <c r="E5" s="10">
+        <v>0.4</v>
+      </c>
+      <c r="F5" s="10">
+        <v>0.4</v>
+      </c>
+      <c r="G5" s="10">
+        <v>0.42</v>
+      </c>
+      <c r="H5" s="10">
+        <v>0.45</v>
+      </c>
+      <c r="I5" s="10">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">Other taxes</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Expense</t>
         </is>
       </c>
-      <c r="C5" s="10">
+      <c r="C6" s="10">
         <v>0.11</v>
       </c>
-      <c r="D5" s="10">
+      <c r="D6" s="10">
         <v>0.09</v>
       </c>
-      <c r="E5" s="10">
+      <c r="E6" s="10">
         <v>0.18</v>
       </c>
-      <c r="F5" s="10">
+      <c r="F6" s="10">
         <v>0.21</v>
       </c>
-      <c r="G5" s="10">
+      <c r="G6" s="10">
         <v>0.1</v>
       </c>
-      <c r="H5" s="10">
+      <c r="H6" s="10">
         <v>0.08</v>
       </c>
-      <c r="I5" s="10">
+      <c r="I6" s="10">
         <v>0.19</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Total O&amp;M costs</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Calculated</t>
         </is>
       </c>
-      <c r="C6" s="15">
+      <c r="C7" s="15">
         <f>SUMIF($B$2:$B$200,"Expense",C$2:C$200)</f>
         <v>2.43</v>
       </c>
-      <c r="D6" s="15">
+      <c r="D7" s="15">
         <f>SUMIF($B$2:$B$200,"Expense",D$2:D$200)</f>
         <v>2.5</v>
       </c>
-      <c r="E6" s="15">
+      <c r="E7" s="15">
         <f>SUMIF($B$2:$B$200,"Expense",E$2:E$200)</f>
         <v>2.66</v>
       </c>
-      <c r="F6" s="15">
+      <c r="F7" s="15">
         <f>SUMIF($B$2:$B$200,"Expense",F$2:F$200)</f>
         <v>2.78</v>
       </c>
-      <c r="G6" s="15">
+      <c r="G7" s="15">
         <f>SUMIF($B$2:$B$200,"Expense",G$2:G$200)</f>
         <v>2.55</v>
       </c>
-      <c r="H6" s="15">
+      <c r="H7" s="15">
         <f>SUMIF($B$2:$B$200,"Expense",H$2:H$200)</f>
         <v>2.64</v>
       </c>
-      <c r="I6" s="15">
+      <c r="I7" s="15">
         <f>SUMIF($B$2:$B$200,"Expense",I$2:I$200)</f>
         <v>2.83</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">CFADS</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Calculated</t>
         </is>
       </c>
-      <c r="C7" s="15">
+      <c r="C8" s="15">
         <f>SUMIF($B$2:$B$200,"Revenue",C$2:C$200)-SUMIF($B$2:$B$200,"Expense",C$2:C$200)</f>
         <v>2.88</v>
       </c>
-      <c r="D7" s="15">
+      <c r="D8" s="15">
         <f>SUMIF($B$2:$B$200,"Revenue",D$2:D$200)-SUMIF($B$2:$B$200,"Expense",D$2:D$200)</f>
         <v>3.12</v>
       </c>
-      <c r="E7" s="15">
+      <c r="E8" s="15">
         <f>SUMIF($B$2:$B$200,"Revenue",E$2:E$200)-SUMIF($B$2:$B$200,"Expense",E$2:E$200)</f>
         <v>7.38</v>
       </c>
-      <c r="F7" s="15">
+      <c r="F8" s="15">
         <f>SUMIF($B$2:$B$200,"Revenue",F$2:F$200)-SUMIF($B$2:$B$200,"Expense",F$2:F$200)</f>
         <v>7.74</v>
       </c>
-      <c r="G7" s="15">
+      <c r="G8" s="15">
         <f>SUMIF($B$2:$B$200,"Revenue",G$2:G$200)-SUMIF($B$2:$B$200,"Expense",G$2:G$200)</f>
         <v>3.38</v>
       </c>
-      <c r="H7" s="15">
+      <c r="H8" s="15">
         <f>SUMIF($B$2:$B$200,"Revenue",H$2:H$200)-SUMIF($B$2:$B$200,"Expense",H$2:H$200)</f>
         <v>3.44</v>
       </c>
-      <c r="I7" s="15">
+      <c r="I8" s="15">
         <f>SUMIF($B$2:$B$200,"Revenue",I$2:I$200)-SUMIF($B$2:$B$200,"Expense",I$2:I$200)</f>
         <v>7.78</v>
       </c>
     </row>
-    <row r="8"/>
-    <row r="9">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Principal</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Debt service</t>
-        </is>
-      </c>
-      <c r="C9" s="10">
-        <v>2.4</v>
-      </c>
-      <c r="D9" s="10">
-        <v>2.42</v>
-      </c>
-      <c r="E9" s="10">
-        <v>2.48</v>
-      </c>
-      <c r="F9" s="10">
-        <v>2.51</v>
-      </c>
-      <c r="G9" s="10">
-        <v>2.57</v>
-      </c>
-      <c r="H9" s="10">
-        <v>2.62</v>
-      </c>
-      <c r="I9" s="10">
-        <v>2.68</v>
-      </c>
-    </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">Principal</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Debt service</t>
+        </is>
+      </c>
+      <c r="C10" s="10">
+        <v>2.4</v>
+      </c>
+      <c r="D10" s="10">
+        <v>2.42</v>
+      </c>
+      <c r="E10" s="10">
+        <v>2.48</v>
+      </c>
+      <c r="F10" s="10">
+        <v>2.51</v>
+      </c>
+      <c r="G10" s="10">
+        <v>2.57</v>
+      </c>
+      <c r="H10" s="10">
+        <v>2.62</v>
+      </c>
+      <c r="I10" s="10">
+        <v>2.68</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">Interest</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Debt service</t>
         </is>
       </c>
-      <c r="C10" s="10">
+      <c r="C11" s="10">
         <v>1.91</v>
       </c>
-      <c r="D10" s="10">
+      <c r="D11" s="10">
         <v>1.86</v>
       </c>
-      <c r="E10" s="10">
+      <c r="E11" s="10">
         <v>1.81</v>
       </c>
-      <c r="F10" s="10">
+      <c r="F11" s="10">
         <v>1.76</v>
       </c>
-      <c r="G10" s="10">
+      <c r="G11" s="10">
         <v>1.7</v>
       </c>
-      <c r="H10" s="10">
+      <c r="H11" s="10">
         <v>1.65</v>
       </c>
-      <c r="I10" s="10">
+      <c r="I11" s="10">
         <v>1.6</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Total debt service costs</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Calculated</t>
         </is>
       </c>
-      <c r="C11" s="15">
+      <c r="C12" s="15">
         <f>SUMIF($B$2:$B$200,"Debt service",C$2:C$200)</f>
         <v>4.31</v>
       </c>
-      <c r="D11" s="15">
+      <c r="D12" s="15">
         <f>SUMIF($B$2:$B$200,"Debt service",D$2:D$200)</f>
         <v>4.28</v>
       </c>
-      <c r="E11" s="15">
+      <c r="E12" s="15">
         <f>SUMIF($B$2:$B$200,"Debt service",E$2:E$200)</f>
         <v>4.29</v>
       </c>
-      <c r="F11" s="15">
+      <c r="F12" s="15">
         <f>SUMIF($B$2:$B$200,"Debt service",F$2:F$200)</f>
         <v>4.27</v>
       </c>
-      <c r="G11" s="15">
+      <c r="G12" s="15">
         <f>SUMIF($B$2:$B$200,"Debt service",G$2:G$200)</f>
         <v>4.27</v>
       </c>
-      <c r="H11" s="15">
+      <c r="H12" s="15">
         <f>SUMIF($B$2:$B$200,"Debt service",H$2:H$200)</f>
         <v>4.27</v>
       </c>
-      <c r="I11" s="15">
+      <c r="I12" s="15">
         <f>SUMIF($B$2:$B$200,"Debt service",I$2:I$200)</f>
         <v>4.28</v>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DSCR - quarter</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Calculated</t>
-        </is>
-      </c>
-      <c r="C13" s="16">
-        <f>IFERROR(C7/C11,"")</f>
-        <v>0.668213</v>
-      </c>
-      <c r="D13" s="16">
-        <f>IFERROR(D7/D11,"")</f>
-        <v>0.728972</v>
-      </c>
-      <c r="E13" s="16">
-        <f>IFERROR(E7/E11,"")</f>
-        <v>1.72028</v>
-      </c>
-      <c r="F13" s="16">
-        <f>IFERROR(F7/F11,"")</f>
-        <v>1.812646</v>
-      </c>
-      <c r="G13" s="16">
-        <f>IFERROR(G7/G11,"")</f>
-        <v>0.791569</v>
-      </c>
-      <c r="H13" s="16">
-        <f>IFERROR(H7/H11,"")</f>
-        <v>0.805621</v>
-      </c>
-      <c r="I13" s="16">
-        <f>IFERROR(I7/I11,"")</f>
-        <v>1.817757</v>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
+          <t xml:space="preserve">DSCR - quarter</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Calculated</t>
+        </is>
+      </c>
+      <c r="C14" s="16">
+        <f>IFERROR(C8/C12,"")</f>
+        <v>0.668213</v>
+      </c>
+      <c r="D14" s="16">
+        <f>IFERROR(D8/D12,"")</f>
+        <v>0.728972</v>
+      </c>
+      <c r="E14" s="16">
+        <f>IFERROR(E8/E12,"")</f>
+        <v>1.72028</v>
+      </c>
+      <c r="F14" s="16">
+        <f>IFERROR(F8/F12,"")</f>
+        <v>1.812646</v>
+      </c>
+      <c r="G14" s="16">
+        <f>IFERROR(G8/G12,"")</f>
+        <v>0.791569</v>
+      </c>
+      <c r="H14" s="16">
+        <f>IFERROR(H8/H12,"")</f>
+        <v>0.805621</v>
+      </c>
+      <c r="I14" s="16">
+        <f>IFERROR(I8/I12,"")</f>
+        <v>1.817757</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
           <t xml:space="preserve">DSCR - LTM</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Calculated</t>
         </is>
       </c>
-      <c r="C14" s="16" t="str">
+      <c r="C15" s="16" t="str">
         <f>""</f>
         <v/>
       </c>
-      <c r="D14" s="16" t="str">
+      <c r="D15" s="16" t="str">
         <f>""</f>
         <v/>
       </c>
-      <c r="E14" s="16" t="str">
+      <c r="E15" s="16" t="str">
         <f>""</f>
         <v/>
       </c>
-      <c r="F14" s="16">
-        <f>IFERROR(SUM(C7:F7)/SUM(C11:F11),"")</f>
+      <c r="F15" s="16">
+        <f>IFERROR(SUM(C8:F8)/SUM(C12:F12),"")</f>
         <v>1.231487</v>
       </c>
-      <c r="G14" s="16">
-        <f>IFERROR(SUM(D7:G7)/SUM(D11:G11),"")</f>
+      <c r="G15" s="16">
+        <f>IFERROR(SUM(D8:G8)/SUM(D12:G12),"")</f>
         <v>1.263589</v>
       </c>
-      <c r="H14" s="16">
-        <f>IFERROR(SUM(E7:H7)/SUM(E11:H11),"")</f>
+      <c r="H15" s="16">
+        <f>IFERROR(SUM(E8:H8)/SUM(E12:H12),"")</f>
         <v>1.283041</v>
       </c>
-      <c r="I14" s="16">
-        <f>IFERROR(SUM(F7:I7)/SUM(F11:I11),"")</f>
+      <c r="I15" s="16">
+        <f>IFERROR(SUM(F8:I8)/SUM(F12:I12),"")</f>
         <v>1.307197</v>
       </c>
     </row>

--- a/dashboard-builder/Bluefield-Example-Inputs.xlsx
+++ b/dashboard-builder/Bluefield-Example-Inputs.xlsx
@@ -363,90 +363,104 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Debt Service  -  quarterly cash flow for page 2.  One column per quarter, oldest on the left.  Role: Revenue, Expense or Debt service.</t>
+          <t xml:space="preserve">Debt Service  -  a running quarterly history for page 2: one column per quarter (Q1 2024 to Q4 2027).  Fill in each quarter when it closes;</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">               Enter expenses and debt service as positive numbers.  The black "Calculated" rows do the math: Total O&amp;M costs = all Expense</t>
+          <t xml:space="preserve">               nothing ever needs shifting.  Page 2 shows the last completed quarter before the Current month's quarter and the 3 before it</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">               rows; CFADS = Revenue - Total O&amp;M costs; Total debt service costs = all Debt service rows; DSCR = CFADS / debt service;</t>
+          <t xml:space="preserve">               (Current month Aug -&gt; through Q2; Dec -&gt; through Q3).  Add more quarters by adding columns with labels like "Q1 2028".</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">               DSCR - LTM = last 4 quarters of CFADS / last 4 quarters of debt service.  To add a line (e.g. LC fees), insert a row</t>
+          <t xml:space="preserve">               Role: Revenue, Expense or Debt service.  Enter expenses and debt service as positive numbers.  The black "Calculated</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">               anywhere and set its Role; the totals pick it up.  The PDF recalculates from the input rows, so it always matches.</t>
+          <t xml:space="preserve">               rows do the math: Total O&amp;M costs, CFADS = Revenue - Total O&amp;M costs, Total debt service costs, DSCR, and DSCR - LTM</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reserves  -  one row per reserve account (DSR, O&amp;M reserve, ...): Required balance and Balance available.  Shown on page 2 below the DSCR chart</t>
+          <t xml:space="preserve">               (last 4 quarters of CFADS / last 4 quarters of debt service).  To add a line (e.g. LC fees), insert the row between two</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">               with the % funded; anything under 100% is flagged.</t>
+          <t xml:space="preserve">               rows of the same block so the totals' ranges grow to include it.  The PDF recalculates from the input rows.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t xml:space="preserve">Reserves  -  one row per reserve account (DSR, O&amp;M reserve, ...): Required balance and Balance available.  Shown on page 2 below the DSCR chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">               with the % funded; anything under 100% is flagged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t xml:space="preserve">DSCR Notes  -  optional Heading + Text pairs shown on page 2 below the reserves.</t>
         </is>
       </c>
     </row>
-    <row r="37"/>
-    <row r="38">
-      <c r="A38" s="6" t="inlineStr">
+    <row r="39"/>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Tips</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-  Do not rename the tabs or the column headers in row 1.  You can add, delete or reorder rows freely.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-  Copy this workbook for each asset (one workbook = one dashboard).</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">-  The Chart dropdowns list the names on the Charts tab automatically (from a hidden "Lists" tab).  Add a chart there and it appears in the dropdowns.</t>
+          <t xml:space="preserve">-  Do not rename the tabs or the column headers in row 1.  You can add, delete or reorder rows freely.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-  Copy this workbook for each asset (one workbook = one dashboard).</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-  The Chart dropdowns list the names on the Charts tab automatically (from a hidden "Lists" tab).  Add a chart there and it appears in the dropdowns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
         <is>
           <t xml:space="preserve">-  Your data never leaves your computer: the builder page reads the file locally in the browser.</t>
         </is>
@@ -2595,13 +2609,22 @@
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="11" customWidth="1"/>
-    <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="11" customWidth="1"/>
-    <col min="9" max="9" width="11" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="10" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="10" customWidth="1"/>
+    <col min="11" max="11" width="10" customWidth="1"/>
+    <col min="12" max="12" width="10" customWidth="1"/>
+    <col min="13" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10" customWidth="1"/>
+    <col min="15" max="15" width="10" customWidth="1"/>
+    <col min="16" max="16" width="10" customWidth="1"/>
+    <col min="17" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="10" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2617,37 +2640,82 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Q1 2024</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q2 2024</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q3 2024</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Q4 2024</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Q1 2025</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Q2 2025</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Q3 2025</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Q4 2025</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Q1 2026</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Q2 2026</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q3 2026</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q4 2026</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q1 2027</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q2 2027</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q3 2027</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q4 2027</t>
         </is>
       </c>
     </row>
@@ -2662,27 +2730,38 @@
           <t xml:space="preserve">Revenue</t>
         </is>
       </c>
-      <c r="C2" s="10">
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10">
         <v>5.31</v>
       </c>
-      <c r="D2" s="10">
+      <c r="G2" s="10">
         <v>5.62</v>
       </c>
-      <c r="E2" s="10">
+      <c r="H2" s="10">
         <v>10.04</v>
       </c>
-      <c r="F2" s="10">
+      <c r="I2" s="10">
         <v>10.52</v>
       </c>
-      <c r="G2" s="10">
+      <c r="J2" s="10">
         <v>5.93</v>
       </c>
-      <c r="H2" s="10">
+      <c r="K2" s="10">
         <v>6.08</v>
       </c>
-      <c r="I2" s="10">
+      <c r="L2" s="10">
         <v>10.61</v>
       </c>
+      <c r="M2" s="10">
+        <v>10.94</v>
+      </c>
+      <c r="N2" s="10"/>
+      <c r="O2" s="10"/>
+      <c r="P2" s="10"/>
+      <c r="Q2" s="10"/>
+      <c r="R2" s="10"/>
     </row>
     <row r="3"/>
     <row r="4">
@@ -2696,27 +2775,38 @@
           <t xml:space="preserve">Expense</t>
         </is>
       </c>
-      <c r="C4" s="10">
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10">
         <v>1.92</v>
       </c>
-      <c r="D4" s="10">
+      <c r="G4" s="10">
         <v>2.01</v>
       </c>
-      <c r="E4" s="10">
+      <c r="H4" s="10">
         <v>2.08</v>
       </c>
-      <c r="F4" s="10">
+      <c r="I4" s="10">
         <v>2.17</v>
       </c>
-      <c r="G4" s="10">
+      <c r="J4" s="10">
         <v>2.03</v>
       </c>
-      <c r="H4" s="10">
+      <c r="K4" s="10">
         <v>2.11</v>
       </c>
-      <c r="I4" s="10">
+      <c r="L4" s="10">
         <v>2.19</v>
       </c>
+      <c r="M4" s="10">
+        <v>2.24</v>
+      </c>
+      <c r="N4" s="10"/>
+      <c r="O4" s="10"/>
+      <c r="P4" s="10"/>
+      <c r="Q4" s="10"/>
+      <c r="R4" s="10"/>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
@@ -2729,27 +2819,38 @@
           <t xml:space="preserve">Expense</t>
         </is>
       </c>
-      <c r="C5" s="10">
-        <v>0.4</v>
-      </c>
-      <c r="D5" s="10">
-        <v>0.4</v>
-      </c>
-      <c r="E5" s="10">
-        <v>0.4</v>
-      </c>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
       <c r="F5" s="10">
         <v>0.4</v>
       </c>
       <c r="G5" s="10">
+        <v>0.4</v>
+      </c>
+      <c r="H5" s="10">
+        <v>0.4</v>
+      </c>
+      <c r="I5" s="10">
+        <v>0.4</v>
+      </c>
+      <c r="J5" s="10">
         <v>0.42</v>
       </c>
-      <c r="H5" s="10">
+      <c r="K5" s="10">
         <v>0.45</v>
       </c>
-      <c r="I5" s="10">
+      <c r="L5" s="10">
         <v>0.45</v>
       </c>
+      <c r="M5" s="10">
+        <v>0.45</v>
+      </c>
+      <c r="N5" s="10"/>
+      <c r="O5" s="10"/>
+      <c r="P5" s="10"/>
+      <c r="Q5" s="10"/>
+      <c r="R5" s="10"/>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
@@ -2762,27 +2863,38 @@
           <t xml:space="preserve">Expense</t>
         </is>
       </c>
-      <c r="C6" s="10">
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10">
         <v>0.11</v>
       </c>
-      <c r="D6" s="10">
+      <c r="G6" s="10">
         <v>0.09</v>
       </c>
-      <c r="E6" s="10">
+      <c r="H6" s="10">
         <v>0.18</v>
       </c>
-      <c r="F6" s="10">
+      <c r="I6" s="10">
         <v>0.21</v>
       </c>
-      <c r="G6" s="10">
+      <c r="J6" s="10">
         <v>0.1</v>
       </c>
-      <c r="H6" s="10">
+      <c r="K6" s="10">
         <v>0.08</v>
       </c>
-      <c r="I6" s="10">
+      <c r="L6" s="10">
         <v>0.19</v>
       </c>
+      <c r="M6" s="10">
+        <v>0.22</v>
+      </c>
+      <c r="N6" s="10"/>
+      <c r="O6" s="10"/>
+      <c r="P6" s="10"/>
+      <c r="Q6" s="10"/>
+      <c r="R6" s="10"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -2795,33 +2907,69 @@
           <t xml:space="preserve">Calculated</t>
         </is>
       </c>
-      <c r="C7" s="15">
-        <f>SUMIF($B$2:$B$200,"Expense",C$2:C$200)</f>
+      <c r="C7" s="15" t="str">
+        <f>IF(COUNT(C2:C3,C4:C6,C10:C11)=0,"",SUM(C4:C6))</f>
+        <v/>
+      </c>
+      <c r="D7" s="15" t="str">
+        <f>IF(COUNT(D2:D3,D4:D6,D10:D11)=0,"",SUM(D4:D6))</f>
+        <v/>
+      </c>
+      <c r="E7" s="15" t="str">
+        <f>IF(COUNT(E2:E3,E4:E6,E10:E11)=0,"",SUM(E4:E6))</f>
+        <v/>
+      </c>
+      <c r="F7" s="15">
+        <f>IF(COUNT(F2:F3,F4:F6,F10:F11)=0,"",SUM(F4:F6))</f>
         <v>2.43</v>
       </c>
-      <c r="D7" s="15">
-        <f>SUMIF($B$2:$B$200,"Expense",D$2:D$200)</f>
+      <c r="G7" s="15">
+        <f>IF(COUNT(G2:G3,G4:G6,G10:G11)=0,"",SUM(G4:G6))</f>
         <v>2.5</v>
       </c>
-      <c r="E7" s="15">
-        <f>SUMIF($B$2:$B$200,"Expense",E$2:E$200)</f>
+      <c r="H7" s="15">
+        <f>IF(COUNT(H2:H3,H4:H6,H10:H11)=0,"",SUM(H4:H6))</f>
         <v>2.66</v>
       </c>
-      <c r="F7" s="15">
-        <f>SUMIF($B$2:$B$200,"Expense",F$2:F$200)</f>
+      <c r="I7" s="15">
+        <f>IF(COUNT(I2:I3,I4:I6,I10:I11)=0,"",SUM(I4:I6))</f>
         <v>2.78</v>
       </c>
-      <c r="G7" s="15">
-        <f>SUMIF($B$2:$B$200,"Expense",G$2:G$200)</f>
+      <c r="J7" s="15">
+        <f>IF(COUNT(J2:J3,J4:J6,J10:J11)=0,"",SUM(J4:J6))</f>
         <v>2.55</v>
       </c>
-      <c r="H7" s="15">
-        <f>SUMIF($B$2:$B$200,"Expense",H$2:H$200)</f>
+      <c r="K7" s="15">
+        <f>IF(COUNT(K2:K3,K4:K6,K10:K11)=0,"",SUM(K4:K6))</f>
         <v>2.64</v>
       </c>
-      <c r="I7" s="15">
-        <f>SUMIF($B$2:$B$200,"Expense",I$2:I$200)</f>
+      <c r="L7" s="15">
+        <f>IF(COUNT(L2:L3,L4:L6,L10:L11)=0,"",SUM(L4:L6))</f>
         <v>2.83</v>
+      </c>
+      <c r="M7" s="15">
+        <f>IF(COUNT(M2:M3,M4:M6,M10:M11)=0,"",SUM(M4:M6))</f>
+        <v>2.91</v>
+      </c>
+      <c r="N7" s="15" t="str">
+        <f>IF(COUNT(N2:N3,N4:N6,N10:N11)=0,"",SUM(N4:N6))</f>
+        <v/>
+      </c>
+      <c r="O7" s="15" t="str">
+        <f>IF(COUNT(O2:O3,O4:O6,O10:O11)=0,"",SUM(O4:O6))</f>
+        <v/>
+      </c>
+      <c r="P7" s="15" t="str">
+        <f>IF(COUNT(P2:P3,P4:P6,P10:P11)=0,"",SUM(P4:P6))</f>
+        <v/>
+      </c>
+      <c r="Q7" s="15" t="str">
+        <f>IF(COUNT(Q2:Q3,Q4:Q6,Q10:Q11)=0,"",SUM(Q4:Q6))</f>
+        <v/>
+      </c>
+      <c r="R7" s="15" t="str">
+        <f>IF(COUNT(R2:R3,R4:R6,R10:R11)=0,"",SUM(R4:R6))</f>
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -2835,33 +2983,69 @@
           <t xml:space="preserve">Calculated</t>
         </is>
       </c>
-      <c r="C8" s="15">
-        <f>SUMIF($B$2:$B$200,"Revenue",C$2:C$200)-SUMIF($B$2:$B$200,"Expense",C$2:C$200)</f>
+      <c r="C8" s="15" t="str">
+        <f>IF(COUNT(C2:C3,C4:C6,C10:C11)=0,"",SUM(C2:C3)-C7)</f>
+        <v/>
+      </c>
+      <c r="D8" s="15" t="str">
+        <f>IF(COUNT(D2:D3,D4:D6,D10:D11)=0,"",SUM(D2:D3)-D7)</f>
+        <v/>
+      </c>
+      <c r="E8" s="15" t="str">
+        <f>IF(COUNT(E2:E3,E4:E6,E10:E11)=0,"",SUM(E2:E3)-E7)</f>
+        <v/>
+      </c>
+      <c r="F8" s="15">
+        <f>IF(COUNT(F2:F3,F4:F6,F10:F11)=0,"",SUM(F2:F3)-F7)</f>
         <v>2.88</v>
       </c>
-      <c r="D8" s="15">
-        <f>SUMIF($B$2:$B$200,"Revenue",D$2:D$200)-SUMIF($B$2:$B$200,"Expense",D$2:D$200)</f>
+      <c r="G8" s="15">
+        <f>IF(COUNT(G2:G3,G4:G6,G10:G11)=0,"",SUM(G2:G3)-G7)</f>
         <v>3.12</v>
       </c>
-      <c r="E8" s="15">
-        <f>SUMIF($B$2:$B$200,"Revenue",E$2:E$200)-SUMIF($B$2:$B$200,"Expense",E$2:E$200)</f>
+      <c r="H8" s="15">
+        <f>IF(COUNT(H2:H3,H4:H6,H10:H11)=0,"",SUM(H2:H3)-H7)</f>
         <v>7.38</v>
       </c>
-      <c r="F8" s="15">
-        <f>SUMIF($B$2:$B$200,"Revenue",F$2:F$200)-SUMIF($B$2:$B$200,"Expense",F$2:F$200)</f>
+      <c r="I8" s="15">
+        <f>IF(COUNT(I2:I3,I4:I6,I10:I11)=0,"",SUM(I2:I3)-I7)</f>
         <v>7.74</v>
       </c>
-      <c r="G8" s="15">
-        <f>SUMIF($B$2:$B$200,"Revenue",G$2:G$200)-SUMIF($B$2:$B$200,"Expense",G$2:G$200)</f>
+      <c r="J8" s="15">
+        <f>IF(COUNT(J2:J3,J4:J6,J10:J11)=0,"",SUM(J2:J3)-J7)</f>
         <v>3.38</v>
       </c>
-      <c r="H8" s="15">
-        <f>SUMIF($B$2:$B$200,"Revenue",H$2:H$200)-SUMIF($B$2:$B$200,"Expense",H$2:H$200)</f>
+      <c r="K8" s="15">
+        <f>IF(COUNT(K2:K3,K4:K6,K10:K11)=0,"",SUM(K2:K3)-K7)</f>
         <v>3.44</v>
       </c>
-      <c r="I8" s="15">
-        <f>SUMIF($B$2:$B$200,"Revenue",I$2:I$200)-SUMIF($B$2:$B$200,"Expense",I$2:I$200)</f>
+      <c r="L8" s="15">
+        <f>IF(COUNT(L2:L3,L4:L6,L10:L11)=0,"",SUM(L2:L3)-L7)</f>
         <v>7.78</v>
+      </c>
+      <c r="M8" s="15">
+        <f>IF(COUNT(M2:M3,M4:M6,M10:M11)=0,"",SUM(M2:M3)-M7)</f>
+        <v>8.03</v>
+      </c>
+      <c r="N8" s="15" t="str">
+        <f>IF(COUNT(N2:N3,N4:N6,N10:N11)=0,"",SUM(N2:N3)-N7)</f>
+        <v/>
+      </c>
+      <c r="O8" s="15" t="str">
+        <f>IF(COUNT(O2:O3,O4:O6,O10:O11)=0,"",SUM(O2:O3)-O7)</f>
+        <v/>
+      </c>
+      <c r="P8" s="15" t="str">
+        <f>IF(COUNT(P2:P3,P4:P6,P10:P11)=0,"",SUM(P2:P3)-P7)</f>
+        <v/>
+      </c>
+      <c r="Q8" s="15" t="str">
+        <f>IF(COUNT(Q2:Q3,Q4:Q6,Q10:Q11)=0,"",SUM(Q2:Q3)-Q7)</f>
+        <v/>
+      </c>
+      <c r="R8" s="15" t="str">
+        <f>IF(COUNT(R2:R3,R4:R6,R10:R11)=0,"",SUM(R2:R3)-R7)</f>
+        <v/>
       </c>
     </row>
     <row r="9"/>
@@ -2876,27 +3060,38 @@
           <t xml:space="preserve">Debt service</t>
         </is>
       </c>
-      <c r="C10" s="10">
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="10">
         <v>2.4</v>
       </c>
-      <c r="D10" s="10">
+      <c r="G10" s="10">
         <v>2.42</v>
       </c>
-      <c r="E10" s="10">
+      <c r="H10" s="10">
         <v>2.48</v>
       </c>
-      <c r="F10" s="10">
+      <c r="I10" s="10">
         <v>2.51</v>
       </c>
-      <c r="G10" s="10">
+      <c r="J10" s="10">
         <v>2.57</v>
       </c>
-      <c r="H10" s="10">
+      <c r="K10" s="10">
         <v>2.62</v>
       </c>
-      <c r="I10" s="10">
+      <c r="L10" s="10">
         <v>2.68</v>
       </c>
+      <c r="M10" s="10">
+        <v>2.74</v>
+      </c>
+      <c r="N10" s="10"/>
+      <c r="O10" s="10"/>
+      <c r="P10" s="10"/>
+      <c r="Q10" s="10"/>
+      <c r="R10" s="10"/>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
@@ -2909,27 +3104,38 @@
           <t xml:space="preserve">Debt service</t>
         </is>
       </c>
-      <c r="C11" s="10">
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10">
         <v>1.91</v>
       </c>
-      <c r="D11" s="10">
+      <c r="G11" s="10">
         <v>1.86</v>
       </c>
-      <c r="E11" s="10">
+      <c r="H11" s="10">
         <v>1.81</v>
       </c>
-      <c r="F11" s="10">
+      <c r="I11" s="10">
         <v>1.76</v>
       </c>
-      <c r="G11" s="10">
+      <c r="J11" s="10">
         <v>1.7</v>
       </c>
-      <c r="H11" s="10">
+      <c r="K11" s="10">
         <v>1.65</v>
       </c>
-      <c r="I11" s="10">
+      <c r="L11" s="10">
         <v>1.6</v>
       </c>
+      <c r="M11" s="10">
+        <v>1.55</v>
+      </c>
+      <c r="N11" s="10"/>
+      <c r="O11" s="10"/>
+      <c r="P11" s="10"/>
+      <c r="Q11" s="10"/>
+      <c r="R11" s="10"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -2942,33 +3148,69 @@
           <t xml:space="preserve">Calculated</t>
         </is>
       </c>
-      <c r="C12" s="15">
-        <f>SUMIF($B$2:$B$200,"Debt service",C$2:C$200)</f>
+      <c r="C12" s="15" t="str">
+        <f>IF(COUNT(C2:C3,C4:C6,C10:C11)=0,"",SUM(C10:C11))</f>
+        <v/>
+      </c>
+      <c r="D12" s="15" t="str">
+        <f>IF(COUNT(D2:D3,D4:D6,D10:D11)=0,"",SUM(D10:D11))</f>
+        <v/>
+      </c>
+      <c r="E12" s="15" t="str">
+        <f>IF(COUNT(E2:E3,E4:E6,E10:E11)=0,"",SUM(E10:E11))</f>
+        <v/>
+      </c>
+      <c r="F12" s="15">
+        <f>IF(COUNT(F2:F3,F4:F6,F10:F11)=0,"",SUM(F10:F11))</f>
         <v>4.31</v>
       </c>
-      <c r="D12" s="15">
-        <f>SUMIF($B$2:$B$200,"Debt service",D$2:D$200)</f>
+      <c r="G12" s="15">
+        <f>IF(COUNT(G2:G3,G4:G6,G10:G11)=0,"",SUM(G10:G11))</f>
         <v>4.28</v>
       </c>
-      <c r="E12" s="15">
-        <f>SUMIF($B$2:$B$200,"Debt service",E$2:E$200)</f>
+      <c r="H12" s="15">
+        <f>IF(COUNT(H2:H3,H4:H6,H10:H11)=0,"",SUM(H10:H11))</f>
         <v>4.29</v>
       </c>
-      <c r="F12" s="15">
-        <f>SUMIF($B$2:$B$200,"Debt service",F$2:F$200)</f>
+      <c r="I12" s="15">
+        <f>IF(COUNT(I2:I3,I4:I6,I10:I11)=0,"",SUM(I10:I11))</f>
         <v>4.27</v>
       </c>
-      <c r="G12" s="15">
-        <f>SUMIF($B$2:$B$200,"Debt service",G$2:G$200)</f>
+      <c r="J12" s="15">
+        <f>IF(COUNT(J2:J3,J4:J6,J10:J11)=0,"",SUM(J10:J11))</f>
         <v>4.27</v>
       </c>
-      <c r="H12" s="15">
-        <f>SUMIF($B$2:$B$200,"Debt service",H$2:H$200)</f>
+      <c r="K12" s="15">
+        <f>IF(COUNT(K2:K3,K4:K6,K10:K11)=0,"",SUM(K10:K11))</f>
         <v>4.27</v>
       </c>
-      <c r="I12" s="15">
-        <f>SUMIF($B$2:$B$200,"Debt service",I$2:I$200)</f>
+      <c r="L12" s="15">
+        <f>IF(COUNT(L2:L3,L4:L6,L10:L11)=0,"",SUM(L10:L11))</f>
         <v>4.28</v>
+      </c>
+      <c r="M12" s="15">
+        <f>IF(COUNT(M2:M3,M4:M6,M10:M11)=0,"",SUM(M10:M11))</f>
+        <v>4.29</v>
+      </c>
+      <c r="N12" s="15" t="str">
+        <f>IF(COUNT(N2:N3,N4:N6,N10:N11)=0,"",SUM(N10:N11))</f>
+        <v/>
+      </c>
+      <c r="O12" s="15" t="str">
+        <f>IF(COUNT(O2:O3,O4:O6,O10:O11)=0,"",SUM(O10:O11))</f>
+        <v/>
+      </c>
+      <c r="P12" s="15" t="str">
+        <f>IF(COUNT(P2:P3,P4:P6,P10:P11)=0,"",SUM(P10:P11))</f>
+        <v/>
+      </c>
+      <c r="Q12" s="15" t="str">
+        <f>IF(COUNT(Q2:Q3,Q4:Q6,Q10:Q11)=0,"",SUM(Q10:Q11))</f>
+        <v/>
+      </c>
+      <c r="R12" s="15" t="str">
+        <f>IF(COUNT(R2:R3,R4:R6,R10:R11)=0,"",SUM(R10:R11))</f>
+        <v/>
       </c>
     </row>
     <row r="13"/>
@@ -2983,33 +3225,69 @@
           <t xml:space="preserve">Calculated</t>
         </is>
       </c>
-      <c r="C14" s="16">
+      <c r="C14" s="16" t="str">
         <f>IFERROR(C8/C12,"")</f>
-        <v>0.668213</v>
-      </c>
-      <c r="D14" s="16">
+        <v/>
+      </c>
+      <c r="D14" s="16" t="str">
         <f>IFERROR(D8/D12,"")</f>
-        <v>0.728972</v>
-      </c>
-      <c r="E14" s="16">
+        <v/>
+      </c>
+      <c r="E14" s="16" t="str">
         <f>IFERROR(E8/E12,"")</f>
-        <v>1.72028</v>
+        <v/>
       </c>
       <c r="F14" s="16">
         <f>IFERROR(F8/F12,"")</f>
-        <v>1.812646</v>
+        <v>0.668213</v>
       </c>
       <c r="G14" s="16">
         <f>IFERROR(G8/G12,"")</f>
-        <v>0.791569</v>
+        <v>0.728972</v>
       </c>
       <c r="H14" s="16">
         <f>IFERROR(H8/H12,"")</f>
-        <v>0.805621</v>
+        <v>1.72028</v>
       </c>
       <c r="I14" s="16">
         <f>IFERROR(I8/I12,"")</f>
+        <v>1.812646</v>
+      </c>
+      <c r="J14" s="16">
+        <f>IFERROR(J8/J12,"")</f>
+        <v>0.791569</v>
+      </c>
+      <c r="K14" s="16">
+        <f>IFERROR(K8/K12,"")</f>
+        <v>0.805621</v>
+      </c>
+      <c r="L14" s="16">
+        <f>IFERROR(L8/L12,"")</f>
         <v>1.817757</v>
+      </c>
+      <c r="M14" s="16">
+        <f>IFERROR(M8/M12,"")</f>
+        <v>1.871795</v>
+      </c>
+      <c r="N14" s="16" t="str">
+        <f>IFERROR(N8/N12,"")</f>
+        <v/>
+      </c>
+      <c r="O14" s="16" t="str">
+        <f>IFERROR(O8/O12,"")</f>
+        <v/>
+      </c>
+      <c r="P14" s="16" t="str">
+        <f>IFERROR(P8/P12,"")</f>
+        <v/>
+      </c>
+      <c r="Q14" s="16" t="str">
+        <f>IFERROR(Q8/Q12,"")</f>
+        <v/>
+      </c>
+      <c r="R14" s="16" t="str">
+        <f>IFERROR(R8/R12,"")</f>
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -3035,21 +3313,57 @@
         <f>""</f>
         <v/>
       </c>
-      <c r="F15" s="16">
-        <f>IFERROR(SUM(C8:F8)/SUM(C12:F12),"")</f>
+      <c r="F15" s="16" t="str">
+        <f>IF(COUNT(C8:F8)&lt;4,"",IFERROR(SUM(C8:F8)/SUM(C12:F12),""))</f>
+        <v/>
+      </c>
+      <c r="G15" s="16" t="str">
+        <f>IF(COUNT(D8:G8)&lt;4,"",IFERROR(SUM(D8:G8)/SUM(D12:G12),""))</f>
+        <v/>
+      </c>
+      <c r="H15" s="16" t="str">
+        <f>IF(COUNT(E8:H8)&lt;4,"",IFERROR(SUM(E8:H8)/SUM(E12:H12),""))</f>
+        <v/>
+      </c>
+      <c r="I15" s="16">
+        <f>IF(COUNT(F8:I8)&lt;4,"",IFERROR(SUM(F8:I8)/SUM(F12:I12),""))</f>
         <v>1.231487</v>
       </c>
-      <c r="G15" s="16">
-        <f>IFERROR(SUM(D8:G8)/SUM(D12:G12),"")</f>
+      <c r="J15" s="16">
+        <f>IF(COUNT(G8:J8)&lt;4,"",IFERROR(SUM(G8:J8)/SUM(G12:J12),""))</f>
         <v>1.263589</v>
       </c>
-      <c r="H15" s="16">
-        <f>IFERROR(SUM(E8:H8)/SUM(E12:H12),"")</f>
+      <c r="K15" s="16">
+        <f>IF(COUNT(H8:K8)&lt;4,"",IFERROR(SUM(H8:K8)/SUM(H12:K12),""))</f>
         <v>1.283041</v>
       </c>
-      <c r="I15" s="16">
-        <f>IFERROR(SUM(F8:I8)/SUM(F12:I12),"")</f>
+      <c r="L15" s="16">
+        <f>IF(COUNT(I8:L8)&lt;4,"",IFERROR(SUM(I8:L8)/SUM(I12:L12),""))</f>
         <v>1.307197</v>
+      </c>
+      <c r="M15" s="16">
+        <f>IF(COUNT(J8:M8)&lt;4,"",IFERROR(SUM(J8:M8)/SUM(J12:M12),""))</f>
+        <v>1.322618</v>
+      </c>
+      <c r="N15" s="16" t="str">
+        <f>IF(COUNT(K8:N8)&lt;4,"",IFERROR(SUM(K8:N8)/SUM(K12:N12),""))</f>
+        <v/>
+      </c>
+      <c r="O15" s="16" t="str">
+        <f>IF(COUNT(L8:O8)&lt;4,"",IFERROR(SUM(L8:O8)/SUM(L12:O12),""))</f>
+        <v/>
+      </c>
+      <c r="P15" s="16" t="str">
+        <f>IF(COUNT(M8:P8)&lt;4,"",IFERROR(SUM(M8:P8)/SUM(M12:P12),""))</f>
+        <v/>
+      </c>
+      <c r="Q15" s="16" t="str">
+        <f>IF(COUNT(N8:Q8)&lt;4,"",IFERROR(SUM(N8:Q8)/SUM(N12:Q12),""))</f>
+        <v/>
+      </c>
+      <c r="R15" s="16" t="str">
+        <f>IF(COUNT(O8:R8)&lt;4,"",IFERROR(SUM(O8:R8)/SUM(O12:R12),""))</f>
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/dashboard-builder/Bluefield-Example-Inputs.xlsx
+++ b/dashboard-builder/Bluefield-Example-Inputs.xlsx
@@ -1579,11 +1579,11 @@
         </is>
       </c>
       <c r="B27" s="8">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">How many of the most recent quarters page 2 shows (1-8).  Enter 3 extra older quarters to show an LTM DSCR for every quarter shown.</t>
+          <t xml:space="preserve">How many of the most recent quarters page 2 shows (1-12), as far as the Debt Service tab has data.  LTM DSCR needs the 3 quarters before each one.</t>
         </is>
       </c>
     </row>
@@ -2730,9 +2730,15 @@
           <t xml:space="preserve">Revenue</t>
         </is>
       </c>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
+      <c r="C2" s="10">
+        <v>5.42</v>
+      </c>
+      <c r="D2" s="10">
+        <v>9.78</v>
+      </c>
+      <c r="E2" s="10">
+        <v>10.21</v>
+      </c>
       <c r="F2" s="10">
         <v>5.31</v>
       </c>
@@ -2775,9 +2781,15 @@
           <t xml:space="preserve">Expense</t>
         </is>
       </c>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
+      <c r="C4" s="10">
+        <v>1.85</v>
+      </c>
+      <c r="D4" s="10">
+        <v>1.95</v>
+      </c>
+      <c r="E4" s="10">
+        <v>2.05</v>
+      </c>
       <c r="F4" s="10">
         <v>1.92</v>
       </c>
@@ -2819,9 +2831,15 @@
           <t xml:space="preserve">Expense</t>
         </is>
       </c>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
+      <c r="C5" s="10">
+        <v>0.38</v>
+      </c>
+      <c r="D5" s="10">
+        <v>0.38</v>
+      </c>
+      <c r="E5" s="10">
+        <v>0.38</v>
+      </c>
       <c r="F5" s="10">
         <v>0.4</v>
       </c>
@@ -2863,9 +2881,15 @@
           <t xml:space="preserve">Expense</t>
         </is>
       </c>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
+      <c r="C6" s="10">
+        <v>0.1</v>
+      </c>
+      <c r="D6" s="10">
+        <v>0.17</v>
+      </c>
+      <c r="E6" s="10">
+        <v>0.2</v>
+      </c>
       <c r="F6" s="10">
         <v>0.11</v>
       </c>
@@ -2907,17 +2931,17 @@
           <t xml:space="preserve">Calculated</t>
         </is>
       </c>
-      <c r="C7" s="15" t="str">
+      <c r="C7" s="15">
         <f>IF(COUNT(C2:C3,C4:C6,C10:C11)=0,"",SUM(C4:C6))</f>
-        <v/>
-      </c>
-      <c r="D7" s="15" t="str">
+        <v>2.33</v>
+      </c>
+      <c r="D7" s="15">
         <f>IF(COUNT(D2:D3,D4:D6,D10:D11)=0,"",SUM(D4:D6))</f>
-        <v/>
-      </c>
-      <c r="E7" s="15" t="str">
+        <v>2.5</v>
+      </c>
+      <c r="E7" s="15">
         <f>IF(COUNT(E2:E3,E4:E6,E10:E11)=0,"",SUM(E4:E6))</f>
-        <v/>
+        <v>2.63</v>
       </c>
       <c r="F7" s="15">
         <f>IF(COUNT(F2:F3,F4:F6,F10:F11)=0,"",SUM(F4:F6))</f>
@@ -2983,17 +3007,17 @@
           <t xml:space="preserve">Calculated</t>
         </is>
       </c>
-      <c r="C8" s="15" t="str">
+      <c r="C8" s="15">
         <f>IF(COUNT(C2:C3,C4:C6,C10:C11)=0,"",SUM(C2:C3)-C7)</f>
-        <v/>
-      </c>
-      <c r="D8" s="15" t="str">
+        <v>3.09</v>
+      </c>
+      <c r="D8" s="15">
         <f>IF(COUNT(D2:D3,D4:D6,D10:D11)=0,"",SUM(D2:D3)-D7)</f>
-        <v/>
-      </c>
-      <c r="E8" s="15" t="str">
+        <v>7.28</v>
+      </c>
+      <c r="E8" s="15">
         <f>IF(COUNT(E2:E3,E4:E6,E10:E11)=0,"",SUM(E2:E3)-E7)</f>
-        <v/>
+        <v>7.58</v>
       </c>
       <c r="F8" s="15">
         <f>IF(COUNT(F2:F3,F4:F6,F10:F11)=0,"",SUM(F2:F3)-F7)</f>
@@ -3060,9 +3084,15 @@
           <t xml:space="preserve">Debt service</t>
         </is>
       </c>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
+      <c r="C10" s="10">
+        <v>2.3</v>
+      </c>
+      <c r="D10" s="10">
+        <v>2.33</v>
+      </c>
+      <c r="E10" s="10">
+        <v>2.37</v>
+      </c>
       <c r="F10" s="10">
         <v>2.4</v>
       </c>
@@ -3104,9 +3134,15 @@
           <t xml:space="preserve">Debt service</t>
         </is>
       </c>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
+      <c r="C11" s="10">
+        <v>2.05</v>
+      </c>
+      <c r="D11" s="10">
+        <v>2</v>
+      </c>
+      <c r="E11" s="10">
+        <v>1.95</v>
+      </c>
       <c r="F11" s="10">
         <v>1.91</v>
       </c>
@@ -3148,17 +3184,17 @@
           <t xml:space="preserve">Calculated</t>
         </is>
       </c>
-      <c r="C12" s="15" t="str">
+      <c r="C12" s="15">
         <f>IF(COUNT(C2:C3,C4:C6,C10:C11)=0,"",SUM(C10:C11))</f>
-        <v/>
-      </c>
-      <c r="D12" s="15" t="str">
+        <v>4.35</v>
+      </c>
+      <c r="D12" s="15">
         <f>IF(COUNT(D2:D3,D4:D6,D10:D11)=0,"",SUM(D10:D11))</f>
-        <v/>
-      </c>
-      <c r="E12" s="15" t="str">
+        <v>4.33</v>
+      </c>
+      <c r="E12" s="15">
         <f>IF(COUNT(E2:E3,E4:E6,E10:E11)=0,"",SUM(E10:E11))</f>
-        <v/>
+        <v>4.32</v>
       </c>
       <c r="F12" s="15">
         <f>IF(COUNT(F2:F3,F4:F6,F10:F11)=0,"",SUM(F10:F11))</f>
@@ -3225,17 +3261,17 @@
           <t xml:space="preserve">Calculated</t>
         </is>
       </c>
-      <c r="C14" s="16" t="str">
+      <c r="C14" s="16">
         <f>IFERROR(C8/C12,"")</f>
-        <v/>
-      </c>
-      <c r="D14" s="16" t="str">
+        <v>0.710345</v>
+      </c>
+      <c r="D14" s="16">
         <f>IFERROR(D8/D12,"")</f>
-        <v/>
-      </c>
-      <c r="E14" s="16" t="str">
+        <v>1.681293</v>
+      </c>
+      <c r="E14" s="16">
         <f>IFERROR(E8/E12,"")</f>
-        <v/>
+        <v>1.75463</v>
       </c>
       <c r="F14" s="16">
         <f>IFERROR(F8/F12,"")</f>
@@ -3313,17 +3349,17 @@
         <f>""</f>
         <v/>
       </c>
-      <c r="F15" s="16" t="str">
+      <c r="F15" s="16">
         <f>IF(COUNT(C8:F8)&lt;4,"",IFERROR(SUM(C8:F8)/SUM(C12:F12),""))</f>
-        <v/>
-      </c>
-      <c r="G15" s="16" t="str">
+        <v>1.203351</v>
+      </c>
+      <c r="G15" s="16">
         <f>IF(COUNT(D8:G8)&lt;4,"",IFERROR(SUM(D8:G8)/SUM(D12:G12),""))</f>
-        <v/>
-      </c>
-      <c r="H15" s="16" t="str">
+        <v>1.209977</v>
+      </c>
+      <c r="H15" s="16">
         <f>IF(COUNT(E8:H8)&lt;4,"",IFERROR(SUM(E8:H8)/SUM(E12:H12),""))</f>
-        <v/>
+        <v>1.218605</v>
       </c>
       <c r="I15" s="16">
         <f>IF(COUNT(F8:I8)&lt;4,"",IFERROR(SUM(F8:I8)/SUM(F12:I12),""))</f>

--- a/dashboard-builder/Bluefield-Example-Inputs.xlsx
+++ b/dashboard-builder/Bluefield-Example-Inputs.xlsx
@@ -2823,7 +2823,7 @@
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Property taxes</t>
+          <t xml:space="preserve">Property and Other Expenses</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
@@ -2832,37 +2832,37 @@
         </is>
       </c>
       <c r="C5" s="10">
-        <v>0.38</v>
+        <v>0.48</v>
       </c>
       <c r="D5" s="10">
-        <v>0.38</v>
+        <v>0.55</v>
       </c>
       <c r="E5" s="10">
-        <v>0.38</v>
+        <v>0.58</v>
       </c>
       <c r="F5" s="10">
-        <v>0.4</v>
+        <v>0.51</v>
       </c>
       <c r="G5" s="10">
-        <v>0.4</v>
+        <v>0.49</v>
       </c>
       <c r="H5" s="10">
-        <v>0.4</v>
+        <v>0.58</v>
       </c>
       <c r="I5" s="10">
-        <v>0.4</v>
+        <v>0.61</v>
       </c>
       <c r="J5" s="10">
-        <v>0.42</v>
+        <v>0.52</v>
       </c>
       <c r="K5" s="10">
-        <v>0.45</v>
+        <v>0.53</v>
       </c>
       <c r="L5" s="10">
-        <v>0.45</v>
+        <v>0.64</v>
       </c>
       <c r="M5" s="10">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="N5" s="10"/>
       <c r="O5" s="10"/>
@@ -2871,59 +2871,85 @@
       <c r="R5" s="10"/>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Other taxes</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Expense</t>
-        </is>
-      </c>
-      <c r="C6" s="10">
-        <v>0.1</v>
-      </c>
-      <c r="D6" s="10">
-        <v>0.17</v>
-      </c>
-      <c r="E6" s="10">
-        <v>0.2</v>
-      </c>
-      <c r="F6" s="10">
-        <v>0.11</v>
-      </c>
-      <c r="G6" s="10">
-        <v>0.09</v>
-      </c>
-      <c r="H6" s="10">
-        <v>0.18</v>
-      </c>
-      <c r="I6" s="10">
-        <v>0.21</v>
-      </c>
-      <c r="J6" s="10">
-        <v>0.1</v>
-      </c>
-      <c r="K6" s="10">
-        <v>0.08</v>
-      </c>
-      <c r="L6" s="10">
-        <v>0.19</v>
-      </c>
-      <c r="M6" s="10">
-        <v>0.22</v>
-      </c>
-      <c r="N6" s="10"/>
-      <c r="O6" s="10"/>
-      <c r="P6" s="10"/>
-      <c r="Q6" s="10"/>
-      <c r="R6" s="10"/>
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Total O&amp;M costs</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Calculated</t>
+        </is>
+      </c>
+      <c r="C6" s="15">
+        <f>IF(COUNT(C2:C3,C4:C5,C9:C10)=0,"",SUM(C4:C5))</f>
+        <v>2.33</v>
+      </c>
+      <c r="D6" s="15">
+        <f>IF(COUNT(D2:D3,D4:D5,D9:D10)=0,"",SUM(D4:D5))</f>
+        <v>2.5</v>
+      </c>
+      <c r="E6" s="15">
+        <f>IF(COUNT(E2:E3,E4:E5,E9:E10)=0,"",SUM(E4:E5))</f>
+        <v>2.63</v>
+      </c>
+      <c r="F6" s="15">
+        <f>IF(COUNT(F2:F3,F4:F5,F9:F10)=0,"",SUM(F4:F5))</f>
+        <v>2.43</v>
+      </c>
+      <c r="G6" s="15">
+        <f>IF(COUNT(G2:G3,G4:G5,G9:G10)=0,"",SUM(G4:G5))</f>
+        <v>2.5</v>
+      </c>
+      <c r="H6" s="15">
+        <f>IF(COUNT(H2:H3,H4:H5,H9:H10)=0,"",SUM(H4:H5))</f>
+        <v>2.66</v>
+      </c>
+      <c r="I6" s="15">
+        <f>IF(COUNT(I2:I3,I4:I5,I9:I10)=0,"",SUM(I4:I5))</f>
+        <v>2.78</v>
+      </c>
+      <c r="J6" s="15">
+        <f>IF(COUNT(J2:J3,J4:J5,J9:J10)=0,"",SUM(J4:J5))</f>
+        <v>2.55</v>
+      </c>
+      <c r="K6" s="15">
+        <f>IF(COUNT(K2:K3,K4:K5,K9:K10)=0,"",SUM(K4:K5))</f>
+        <v>2.64</v>
+      </c>
+      <c r="L6" s="15">
+        <f>IF(COUNT(L2:L3,L4:L5,L9:L10)=0,"",SUM(L4:L5))</f>
+        <v>2.83</v>
+      </c>
+      <c r="M6" s="15">
+        <f>IF(COUNT(M2:M3,M4:M5,M9:M10)=0,"",SUM(M4:M5))</f>
+        <v>2.91</v>
+      </c>
+      <c r="N6" s="15" t="str">
+        <f>IF(COUNT(N2:N3,N4:N5,N9:N10)=0,"",SUM(N4:N5))</f>
+        <v/>
+      </c>
+      <c r="O6" s="15" t="str">
+        <f>IF(COUNT(O2:O3,O4:O5,O9:O10)=0,"",SUM(O4:O5))</f>
+        <v/>
+      </c>
+      <c r="P6" s="15" t="str">
+        <f>IF(COUNT(P2:P3,P4:P5,P9:P10)=0,"",SUM(P4:P5))</f>
+        <v/>
+      </c>
+      <c r="Q6" s="15" t="str">
+        <f>IF(COUNT(Q2:Q3,Q4:Q5,Q9:Q10)=0,"",SUM(Q4:Q5))</f>
+        <v/>
+      </c>
+      <c r="R6" s="15" t="str">
+        <f>IF(COUNT(R2:R3,R4:R5,R9:R10)=0,"",SUM(R4:R5))</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Total O&amp;M costs</t>
+          <t xml:space="preserve">CFADS</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -2932,151 +2958,125 @@
         </is>
       </c>
       <c r="C7" s="15">
-        <f>IF(COUNT(C2:C3,C4:C6,C10:C11)=0,"",SUM(C4:C6))</f>
+        <f>IF(COUNT(C2:C3,C4:C5,C9:C10)=0,"",SUM(C2:C3)-C6)</f>
+        <v>3.09</v>
+      </c>
+      <c r="D7" s="15">
+        <f>IF(COUNT(D2:D3,D4:D5,D9:D10)=0,"",SUM(D2:D3)-D6)</f>
+        <v>7.28</v>
+      </c>
+      <c r="E7" s="15">
+        <f>IF(COUNT(E2:E3,E4:E5,E9:E10)=0,"",SUM(E2:E3)-E6)</f>
+        <v>7.58</v>
+      </c>
+      <c r="F7" s="15">
+        <f>IF(COUNT(F2:F3,F4:F5,F9:F10)=0,"",SUM(F2:F3)-F6)</f>
+        <v>2.88</v>
+      </c>
+      <c r="G7" s="15">
+        <f>IF(COUNT(G2:G3,G4:G5,G9:G10)=0,"",SUM(G2:G3)-G6)</f>
+        <v>3.12</v>
+      </c>
+      <c r="H7" s="15">
+        <f>IF(COUNT(H2:H3,H4:H5,H9:H10)=0,"",SUM(H2:H3)-H6)</f>
+        <v>7.38</v>
+      </c>
+      <c r="I7" s="15">
+        <f>IF(COUNT(I2:I3,I4:I5,I9:I10)=0,"",SUM(I2:I3)-I6)</f>
+        <v>7.74</v>
+      </c>
+      <c r="J7" s="15">
+        <f>IF(COUNT(J2:J3,J4:J5,J9:J10)=0,"",SUM(J2:J3)-J6)</f>
+        <v>3.38</v>
+      </c>
+      <c r="K7" s="15">
+        <f>IF(COUNT(K2:K3,K4:K5,K9:K10)=0,"",SUM(K2:K3)-K6)</f>
+        <v>3.44</v>
+      </c>
+      <c r="L7" s="15">
+        <f>IF(COUNT(L2:L3,L4:L5,L9:L10)=0,"",SUM(L2:L3)-L6)</f>
+        <v>7.78</v>
+      </c>
+      <c r="M7" s="15">
+        <f>IF(COUNT(M2:M3,M4:M5,M9:M10)=0,"",SUM(M2:M3)-M6)</f>
+        <v>8.03</v>
+      </c>
+      <c r="N7" s="15" t="str">
+        <f>IF(COUNT(N2:N3,N4:N5,N9:N10)=0,"",SUM(N2:N3)-N6)</f>
+        <v/>
+      </c>
+      <c r="O7" s="15" t="str">
+        <f>IF(COUNT(O2:O3,O4:O5,O9:O10)=0,"",SUM(O2:O3)-O6)</f>
+        <v/>
+      </c>
+      <c r="P7" s="15" t="str">
+        <f>IF(COUNT(P2:P3,P4:P5,P9:P10)=0,"",SUM(P2:P3)-P6)</f>
+        <v/>
+      </c>
+      <c r="Q7" s="15" t="str">
+        <f>IF(COUNT(Q2:Q3,Q4:Q5,Q9:Q10)=0,"",SUM(Q2:Q3)-Q6)</f>
+        <v/>
+      </c>
+      <c r="R7" s="15" t="str">
+        <f>IF(COUNT(R2:R3,R4:R5,R9:R10)=0,"",SUM(R2:R3)-R6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8"/>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Principal</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Debt service</t>
+        </is>
+      </c>
+      <c r="C9" s="10">
+        <v>2.3</v>
+      </c>
+      <c r="D9" s="10">
         <v>2.33</v>
       </c>
-      <c r="D7" s="15">
-        <f>IF(COUNT(D2:D3,D4:D6,D10:D11)=0,"",SUM(D4:D6))</f>
-        <v>2.5</v>
-      </c>
-      <c r="E7" s="15">
-        <f>IF(COUNT(E2:E3,E4:E6,E10:E11)=0,"",SUM(E4:E6))</f>
-        <v>2.63</v>
-      </c>
-      <c r="F7" s="15">
-        <f>IF(COUNT(F2:F3,F4:F6,F10:F11)=0,"",SUM(F4:F6))</f>
-        <v>2.43</v>
-      </c>
-      <c r="G7" s="15">
-        <f>IF(COUNT(G2:G3,G4:G6,G10:G11)=0,"",SUM(G4:G6))</f>
-        <v>2.5</v>
-      </c>
-      <c r="H7" s="15">
-        <f>IF(COUNT(H2:H3,H4:H6,H10:H11)=0,"",SUM(H4:H6))</f>
-        <v>2.66</v>
-      </c>
-      <c r="I7" s="15">
-        <f>IF(COUNT(I2:I3,I4:I6,I10:I11)=0,"",SUM(I4:I6))</f>
-        <v>2.78</v>
-      </c>
-      <c r="J7" s="15">
-        <f>IF(COUNT(J2:J3,J4:J6,J10:J11)=0,"",SUM(J4:J6))</f>
-        <v>2.55</v>
-      </c>
-      <c r="K7" s="15">
-        <f>IF(COUNT(K2:K3,K4:K6,K10:K11)=0,"",SUM(K4:K6))</f>
-        <v>2.64</v>
-      </c>
-      <c r="L7" s="15">
-        <f>IF(COUNT(L2:L3,L4:L6,L10:L11)=0,"",SUM(L4:L6))</f>
-        <v>2.83</v>
-      </c>
-      <c r="M7" s="15">
-        <f>IF(COUNT(M2:M3,M4:M6,M10:M11)=0,"",SUM(M4:M6))</f>
-        <v>2.91</v>
-      </c>
-      <c r="N7" s="15" t="str">
-        <f>IF(COUNT(N2:N3,N4:N6,N10:N11)=0,"",SUM(N4:N6))</f>
-        <v/>
-      </c>
-      <c r="O7" s="15" t="str">
-        <f>IF(COUNT(O2:O3,O4:O6,O10:O11)=0,"",SUM(O4:O6))</f>
-        <v/>
-      </c>
-      <c r="P7" s="15" t="str">
-        <f>IF(COUNT(P2:P3,P4:P6,P10:P11)=0,"",SUM(P4:P6))</f>
-        <v/>
-      </c>
-      <c r="Q7" s="15" t="str">
-        <f>IF(COUNT(Q2:Q3,Q4:Q6,Q10:Q11)=0,"",SUM(Q4:Q6))</f>
-        <v/>
-      </c>
-      <c r="R7" s="15" t="str">
-        <f>IF(COUNT(R2:R3,R4:R6,R10:R11)=0,"",SUM(R4:R6))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CFADS</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Calculated</t>
-        </is>
-      </c>
-      <c r="C8" s="15">
-        <f>IF(COUNT(C2:C3,C4:C6,C10:C11)=0,"",SUM(C2:C3)-C7)</f>
-        <v>3.09</v>
-      </c>
-      <c r="D8" s="15">
-        <f>IF(COUNT(D2:D3,D4:D6,D10:D11)=0,"",SUM(D2:D3)-D7)</f>
-        <v>7.28</v>
-      </c>
-      <c r="E8" s="15">
-        <f>IF(COUNT(E2:E3,E4:E6,E10:E11)=0,"",SUM(E2:E3)-E7)</f>
-        <v>7.58</v>
-      </c>
-      <c r="F8" s="15">
-        <f>IF(COUNT(F2:F3,F4:F6,F10:F11)=0,"",SUM(F2:F3)-F7)</f>
-        <v>2.88</v>
-      </c>
-      <c r="G8" s="15">
-        <f>IF(COUNT(G2:G3,G4:G6,G10:G11)=0,"",SUM(G2:G3)-G7)</f>
-        <v>3.12</v>
-      </c>
-      <c r="H8" s="15">
-        <f>IF(COUNT(H2:H3,H4:H6,H10:H11)=0,"",SUM(H2:H3)-H7)</f>
-        <v>7.38</v>
-      </c>
-      <c r="I8" s="15">
-        <f>IF(COUNT(I2:I3,I4:I6,I10:I11)=0,"",SUM(I2:I3)-I7)</f>
-        <v>7.74</v>
-      </c>
-      <c r="J8" s="15">
-        <f>IF(COUNT(J2:J3,J4:J6,J10:J11)=0,"",SUM(J2:J3)-J7)</f>
-        <v>3.38</v>
-      </c>
-      <c r="K8" s="15">
-        <f>IF(COUNT(K2:K3,K4:K6,K10:K11)=0,"",SUM(K2:K3)-K7)</f>
-        <v>3.44</v>
-      </c>
-      <c r="L8" s="15">
-        <f>IF(COUNT(L2:L3,L4:L6,L10:L11)=0,"",SUM(L2:L3)-L7)</f>
-        <v>7.78</v>
-      </c>
-      <c r="M8" s="15">
-        <f>IF(COUNT(M2:M3,M4:M6,M10:M11)=0,"",SUM(M2:M3)-M7)</f>
-        <v>8.03</v>
-      </c>
-      <c r="N8" s="15" t="str">
-        <f>IF(COUNT(N2:N3,N4:N6,N10:N11)=0,"",SUM(N2:N3)-N7)</f>
-        <v/>
-      </c>
-      <c r="O8" s="15" t="str">
-        <f>IF(COUNT(O2:O3,O4:O6,O10:O11)=0,"",SUM(O2:O3)-O7)</f>
-        <v/>
-      </c>
-      <c r="P8" s="15" t="str">
-        <f>IF(COUNT(P2:P3,P4:P6,P10:P11)=0,"",SUM(P2:P3)-P7)</f>
-        <v/>
-      </c>
-      <c r="Q8" s="15" t="str">
-        <f>IF(COUNT(Q2:Q3,Q4:Q6,Q10:Q11)=0,"",SUM(Q2:Q3)-Q7)</f>
-        <v/>
-      </c>
-      <c r="R8" s="15" t="str">
-        <f>IF(COUNT(R2:R3,R4:R6,R10:R11)=0,"",SUM(R2:R3)-R7)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9"/>
+      <c r="E9" s="10">
+        <v>2.37</v>
+      </c>
+      <c r="F9" s="10">
+        <v>2.4</v>
+      </c>
+      <c r="G9" s="10">
+        <v>2.42</v>
+      </c>
+      <c r="H9" s="10">
+        <v>2.48</v>
+      </c>
+      <c r="I9" s="10">
+        <v>2.51</v>
+      </c>
+      <c r="J9" s="10">
+        <v>2.57</v>
+      </c>
+      <c r="K9" s="10">
+        <v>2.62</v>
+      </c>
+      <c r="L9" s="10">
+        <v>2.68</v>
+      </c>
+      <c r="M9" s="10">
+        <v>2.74</v>
+      </c>
+      <c r="N9" s="10"/>
+      <c r="O9" s="10"/>
+      <c r="P9" s="10"/>
+      <c r="Q9" s="10"/>
+      <c r="R9" s="10"/>
+    </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Principal</t>
+          <t xml:space="preserve">Interest</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
@@ -3085,37 +3085,37 @@
         </is>
       </c>
       <c r="C10" s="10">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="D10" s="10">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="E10" s="10">
-        <v>2.37</v>
+        <v>1.95</v>
       </c>
       <c r="F10" s="10">
-        <v>2.4</v>
+        <v>1.91</v>
       </c>
       <c r="G10" s="10">
-        <v>2.42</v>
+        <v>1.86</v>
       </c>
       <c r="H10" s="10">
-        <v>2.48</v>
+        <v>1.81</v>
       </c>
       <c r="I10" s="10">
-        <v>2.51</v>
+        <v>1.76</v>
       </c>
       <c r="J10" s="10">
-        <v>2.57</v>
+        <v>1.7</v>
       </c>
       <c r="K10" s="10">
-        <v>2.62</v>
+        <v>1.65</v>
       </c>
       <c r="L10" s="10">
-        <v>2.68</v>
+        <v>1.6</v>
       </c>
       <c r="M10" s="10">
-        <v>2.74</v>
+        <v>1.55</v>
       </c>
       <c r="N10" s="10"/>
       <c r="O10" s="10"/>
@@ -3124,136 +3124,162 @@
       <c r="R10" s="10"/>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Interest</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Debt service</t>
-        </is>
-      </c>
-      <c r="C11" s="10">
-        <v>2.05</v>
-      </c>
-      <c r="D11" s="10">
-        <v>2</v>
-      </c>
-      <c r="E11" s="10">
-        <v>1.95</v>
-      </c>
-      <c r="F11" s="10">
-        <v>1.91</v>
-      </c>
-      <c r="G11" s="10">
-        <v>1.86</v>
-      </c>
-      <c r="H11" s="10">
-        <v>1.81</v>
-      </c>
-      <c r="I11" s="10">
-        <v>1.76</v>
-      </c>
-      <c r="J11" s="10">
-        <v>1.7</v>
-      </c>
-      <c r="K11" s="10">
-        <v>1.65</v>
-      </c>
-      <c r="L11" s="10">
-        <v>1.6</v>
-      </c>
-      <c r="M11" s="10">
-        <v>1.55</v>
-      </c>
-      <c r="N11" s="10"/>
-      <c r="O11" s="10"/>
-      <c r="P11" s="10"/>
-      <c r="Q11" s="10"/>
-      <c r="R11" s="10"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Total debt service costs</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Calculated</t>
         </is>
       </c>
-      <c r="C12" s="15">
-        <f>IF(COUNT(C2:C3,C4:C6,C10:C11)=0,"",SUM(C10:C11))</f>
+      <c r="C11" s="15">
+        <f>IF(COUNT(C2:C3,C4:C5,C9:C10)=0,"",SUM(C9:C10))</f>
         <v>4.35</v>
       </c>
-      <c r="D12" s="15">
-        <f>IF(COUNT(D2:D3,D4:D6,D10:D11)=0,"",SUM(D10:D11))</f>
+      <c r="D11" s="15">
+        <f>IF(COUNT(D2:D3,D4:D5,D9:D10)=0,"",SUM(D9:D10))</f>
         <v>4.33</v>
       </c>
-      <c r="E12" s="15">
-        <f>IF(COUNT(E2:E3,E4:E6,E10:E11)=0,"",SUM(E10:E11))</f>
+      <c r="E11" s="15">
+        <f>IF(COUNT(E2:E3,E4:E5,E9:E10)=0,"",SUM(E9:E10))</f>
         <v>4.32</v>
       </c>
-      <c r="F12" s="15">
-        <f>IF(COUNT(F2:F3,F4:F6,F10:F11)=0,"",SUM(F10:F11))</f>
+      <c r="F11" s="15">
+        <f>IF(COUNT(F2:F3,F4:F5,F9:F10)=0,"",SUM(F9:F10))</f>
         <v>4.31</v>
       </c>
-      <c r="G12" s="15">
-        <f>IF(COUNT(G2:G3,G4:G6,G10:G11)=0,"",SUM(G10:G11))</f>
+      <c r="G11" s="15">
+        <f>IF(COUNT(G2:G3,G4:G5,G9:G10)=0,"",SUM(G9:G10))</f>
         <v>4.28</v>
       </c>
-      <c r="H12" s="15">
-        <f>IF(COUNT(H2:H3,H4:H6,H10:H11)=0,"",SUM(H10:H11))</f>
+      <c r="H11" s="15">
+        <f>IF(COUNT(H2:H3,H4:H5,H9:H10)=0,"",SUM(H9:H10))</f>
         <v>4.29</v>
       </c>
-      <c r="I12" s="15">
-        <f>IF(COUNT(I2:I3,I4:I6,I10:I11)=0,"",SUM(I10:I11))</f>
+      <c r="I11" s="15">
+        <f>IF(COUNT(I2:I3,I4:I5,I9:I10)=0,"",SUM(I9:I10))</f>
         <v>4.27</v>
       </c>
-      <c r="J12" s="15">
-        <f>IF(COUNT(J2:J3,J4:J6,J10:J11)=0,"",SUM(J10:J11))</f>
+      <c r="J11" s="15">
+        <f>IF(COUNT(J2:J3,J4:J5,J9:J10)=0,"",SUM(J9:J10))</f>
         <v>4.27</v>
       </c>
-      <c r="K12" s="15">
-        <f>IF(COUNT(K2:K3,K4:K6,K10:K11)=0,"",SUM(K10:K11))</f>
+      <c r="K11" s="15">
+        <f>IF(COUNT(K2:K3,K4:K5,K9:K10)=0,"",SUM(K9:K10))</f>
         <v>4.27</v>
       </c>
-      <c r="L12" s="15">
-        <f>IF(COUNT(L2:L3,L4:L6,L10:L11)=0,"",SUM(L10:L11))</f>
+      <c r="L11" s="15">
+        <f>IF(COUNT(L2:L3,L4:L5,L9:L10)=0,"",SUM(L9:L10))</f>
         <v>4.28</v>
       </c>
-      <c r="M12" s="15">
-        <f>IF(COUNT(M2:M3,M4:M6,M10:M11)=0,"",SUM(M10:M11))</f>
+      <c r="M11" s="15">
+        <f>IF(COUNT(M2:M3,M4:M5,M9:M10)=0,"",SUM(M9:M10))</f>
         <v>4.29</v>
       </c>
-      <c r="N12" s="15" t="str">
-        <f>IF(COUNT(N2:N3,N4:N6,N10:N11)=0,"",SUM(N10:N11))</f>
-        <v/>
-      </c>
-      <c r="O12" s="15" t="str">
-        <f>IF(COUNT(O2:O3,O4:O6,O10:O11)=0,"",SUM(O10:O11))</f>
-        <v/>
-      </c>
-      <c r="P12" s="15" t="str">
-        <f>IF(COUNT(P2:P3,P4:P6,P10:P11)=0,"",SUM(P10:P11))</f>
-        <v/>
-      </c>
-      <c r="Q12" s="15" t="str">
-        <f>IF(COUNT(Q2:Q3,Q4:Q6,Q10:Q11)=0,"",SUM(Q10:Q11))</f>
-        <v/>
-      </c>
-      <c r="R12" s="15" t="str">
-        <f>IF(COUNT(R2:R3,R4:R6,R10:R11)=0,"",SUM(R10:R11))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13"/>
+      <c r="N11" s="15" t="str">
+        <f>IF(COUNT(N2:N3,N4:N5,N9:N10)=0,"",SUM(N9:N10))</f>
+        <v/>
+      </c>
+      <c r="O11" s="15" t="str">
+        <f>IF(COUNT(O2:O3,O4:O5,O9:O10)=0,"",SUM(O9:O10))</f>
+        <v/>
+      </c>
+      <c r="P11" s="15" t="str">
+        <f>IF(COUNT(P2:P3,P4:P5,P9:P10)=0,"",SUM(P9:P10))</f>
+        <v/>
+      </c>
+      <c r="Q11" s="15" t="str">
+        <f>IF(COUNT(Q2:Q3,Q4:Q5,Q9:Q10)=0,"",SUM(Q9:Q10))</f>
+        <v/>
+      </c>
+      <c r="R11" s="15" t="str">
+        <f>IF(COUNT(R2:R3,R4:R5,R9:R10)=0,"",SUM(R9:R10))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DSCR - quarter</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Calculated</t>
+        </is>
+      </c>
+      <c r="C13" s="16">
+        <f>IFERROR(C7/C11,"")</f>
+        <v>0.710345</v>
+      </c>
+      <c r="D13" s="16">
+        <f>IFERROR(D7/D11,"")</f>
+        <v>1.681293</v>
+      </c>
+      <c r="E13" s="16">
+        <f>IFERROR(E7/E11,"")</f>
+        <v>1.75463</v>
+      </c>
+      <c r="F13" s="16">
+        <f>IFERROR(F7/F11,"")</f>
+        <v>0.668213</v>
+      </c>
+      <c r="G13" s="16">
+        <f>IFERROR(G7/G11,"")</f>
+        <v>0.728972</v>
+      </c>
+      <c r="H13" s="16">
+        <f>IFERROR(H7/H11,"")</f>
+        <v>1.72028</v>
+      </c>
+      <c r="I13" s="16">
+        <f>IFERROR(I7/I11,"")</f>
+        <v>1.812646</v>
+      </c>
+      <c r="J13" s="16">
+        <f>IFERROR(J7/J11,"")</f>
+        <v>0.791569</v>
+      </c>
+      <c r="K13" s="16">
+        <f>IFERROR(K7/K11,"")</f>
+        <v>0.805621</v>
+      </c>
+      <c r="L13" s="16">
+        <f>IFERROR(L7/L11,"")</f>
+        <v>1.817757</v>
+      </c>
+      <c r="M13" s="16">
+        <f>IFERROR(M7/M11,"")</f>
+        <v>1.871795</v>
+      </c>
+      <c r="N13" s="16" t="str">
+        <f>IFERROR(N7/N11,"")</f>
+        <v/>
+      </c>
+      <c r="O13" s="16" t="str">
+        <f>IFERROR(O7/O11,"")</f>
+        <v/>
+      </c>
+      <c r="P13" s="16" t="str">
+        <f>IFERROR(P7/P11,"")</f>
+        <v/>
+      </c>
+      <c r="Q13" s="16" t="str">
+        <f>IFERROR(Q7/Q11,"")</f>
+        <v/>
+      </c>
+      <c r="R13" s="16" t="str">
+        <f>IFERROR(R7/R11,"")</f>
+        <v/>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">DSCR - quarter</t>
+          <t xml:space="preserve">DSCR - LTM</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -3261,144 +3287,68 @@
           <t xml:space="preserve">Calculated</t>
         </is>
       </c>
-      <c r="C14" s="16">
-        <f>IFERROR(C8/C12,"")</f>
-        <v>0.710345</v>
-      </c>
-      <c r="D14" s="16">
-        <f>IFERROR(D8/D12,"")</f>
-        <v>1.681293</v>
-      </c>
-      <c r="E14" s="16">
-        <f>IFERROR(E8/E12,"")</f>
-        <v>1.75463</v>
+      <c r="C14" s="16" t="str">
+        <f>""</f>
+        <v/>
+      </c>
+      <c r="D14" s="16" t="str">
+        <f>""</f>
+        <v/>
+      </c>
+      <c r="E14" s="16" t="str">
+        <f>""</f>
+        <v/>
       </c>
       <c r="F14" s="16">
-        <f>IFERROR(F8/F12,"")</f>
-        <v>0.668213</v>
+        <f>IF(COUNT(C7:F7)&lt;4,"",IFERROR(SUM(C7:F7)/SUM(C11:F11),""))</f>
+        <v>1.203351</v>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(G8/G12,"")</f>
-        <v>0.728972</v>
+        <f>IF(COUNT(D7:G7)&lt;4,"",IFERROR(SUM(D7:G7)/SUM(D11:G11),""))</f>
+        <v>1.209977</v>
       </c>
       <c r="H14" s="16">
-        <f>IFERROR(H8/H12,"")</f>
-        <v>1.72028</v>
+        <f>IF(COUNT(E7:H7)&lt;4,"",IFERROR(SUM(E7:H7)/SUM(E11:H11),""))</f>
+        <v>1.218605</v>
       </c>
       <c r="I14" s="16">
-        <f>IFERROR(I8/I12,"")</f>
-        <v>1.812646</v>
+        <f>IF(COUNT(F7:I7)&lt;4,"",IFERROR(SUM(F7:I7)/SUM(F11:I11),""))</f>
+        <v>1.231487</v>
       </c>
       <c r="J14" s="16">
-        <f>IFERROR(J8/J12,"")</f>
-        <v>0.791569</v>
+        <f>IF(COUNT(G7:J7)&lt;4,"",IFERROR(SUM(G7:J7)/SUM(G11:J11),""))</f>
+        <v>1.263589</v>
       </c>
       <c r="K14" s="16">
-        <f>IFERROR(K8/K12,"")</f>
-        <v>0.805621</v>
+        <f>IF(COUNT(H7:K7)&lt;4,"",IFERROR(SUM(H7:K7)/SUM(H11:K11),""))</f>
+        <v>1.283041</v>
       </c>
       <c r="L14" s="16">
-        <f>IFERROR(L8/L12,"")</f>
-        <v>1.817757</v>
+        <f>IF(COUNT(I7:L7)&lt;4,"",IFERROR(SUM(I7:L7)/SUM(I11:L11),""))</f>
+        <v>1.307197</v>
       </c>
       <c r="M14" s="16">
-        <f>IFERROR(M8/M12,"")</f>
-        <v>1.871795</v>
+        <f>IF(COUNT(J7:M7)&lt;4,"",IFERROR(SUM(J7:M7)/SUM(J11:M11),""))</f>
+        <v>1.322618</v>
       </c>
       <c r="N14" s="16" t="str">
-        <f>IFERROR(N8/N12,"")</f>
+        <f>IF(COUNT(K7:N7)&lt;4,"",IFERROR(SUM(K7:N7)/SUM(K11:N11),""))</f>
         <v/>
       </c>
       <c r="O14" s="16" t="str">
-        <f>IFERROR(O8/O12,"")</f>
+        <f>IF(COUNT(L7:O7)&lt;4,"",IFERROR(SUM(L7:O7)/SUM(L11:O11),""))</f>
         <v/>
       </c>
       <c r="P14" s="16" t="str">
-        <f>IFERROR(P8/P12,"")</f>
+        <f>IF(COUNT(M7:P7)&lt;4,"",IFERROR(SUM(M7:P7)/SUM(M11:P11),""))</f>
         <v/>
       </c>
       <c r="Q14" s="16" t="str">
-        <f>IFERROR(Q8/Q12,"")</f>
+        <f>IF(COUNT(N7:Q7)&lt;4,"",IFERROR(SUM(N7:Q7)/SUM(N11:Q11),""))</f>
         <v/>
       </c>
       <c r="R14" s="16" t="str">
-        <f>IFERROR(R8/R12,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DSCR - LTM</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Calculated</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="str">
-        <f>""</f>
-        <v/>
-      </c>
-      <c r="D15" s="16" t="str">
-        <f>""</f>
-        <v/>
-      </c>
-      <c r="E15" s="16" t="str">
-        <f>""</f>
-        <v/>
-      </c>
-      <c r="F15" s="16">
-        <f>IF(COUNT(C8:F8)&lt;4,"",IFERROR(SUM(C8:F8)/SUM(C12:F12),""))</f>
-        <v>1.203351</v>
-      </c>
-      <c r="G15" s="16">
-        <f>IF(COUNT(D8:G8)&lt;4,"",IFERROR(SUM(D8:G8)/SUM(D12:G12),""))</f>
-        <v>1.209977</v>
-      </c>
-      <c r="H15" s="16">
-        <f>IF(COUNT(E8:H8)&lt;4,"",IFERROR(SUM(E8:H8)/SUM(E12:H12),""))</f>
-        <v>1.218605</v>
-      </c>
-      <c r="I15" s="16">
-        <f>IF(COUNT(F8:I8)&lt;4,"",IFERROR(SUM(F8:I8)/SUM(F12:I12),""))</f>
-        <v>1.231487</v>
-      </c>
-      <c r="J15" s="16">
-        <f>IF(COUNT(G8:J8)&lt;4,"",IFERROR(SUM(G8:J8)/SUM(G12:J12),""))</f>
-        <v>1.263589</v>
-      </c>
-      <c r="K15" s="16">
-        <f>IF(COUNT(H8:K8)&lt;4,"",IFERROR(SUM(H8:K8)/SUM(H12:K12),""))</f>
-        <v>1.283041</v>
-      </c>
-      <c r="L15" s="16">
-        <f>IF(COUNT(I8:L8)&lt;4,"",IFERROR(SUM(I8:L8)/SUM(I12:L12),""))</f>
-        <v>1.307197</v>
-      </c>
-      <c r="M15" s="16">
-        <f>IF(COUNT(J8:M8)&lt;4,"",IFERROR(SUM(J8:M8)/SUM(J12:M12),""))</f>
-        <v>1.322618</v>
-      </c>
-      <c r="N15" s="16" t="str">
-        <f>IF(COUNT(K8:N8)&lt;4,"",IFERROR(SUM(K8:N8)/SUM(K12:N12),""))</f>
-        <v/>
-      </c>
-      <c r="O15" s="16" t="str">
-        <f>IF(COUNT(L8:O8)&lt;4,"",IFERROR(SUM(L8:O8)/SUM(L12:O12),""))</f>
-        <v/>
-      </c>
-      <c r="P15" s="16" t="str">
-        <f>IF(COUNT(M8:P8)&lt;4,"",IFERROR(SUM(M8:P8)/SUM(M12:P12),""))</f>
-        <v/>
-      </c>
-      <c r="Q15" s="16" t="str">
-        <f>IF(COUNT(N8:Q8)&lt;4,"",IFERROR(SUM(N8:Q8)/SUM(N12:Q12),""))</f>
-        <v/>
-      </c>
-      <c r="R15" s="16" t="str">
-        <f>IF(COUNT(O8:R8)&lt;4,"",IFERROR(SUM(O8:R8)/SUM(O12:R12),""))</f>
+        <f>IF(COUNT(O7:R7)&lt;4,"",IFERROR(SUM(O7:R7)/SUM(O11:R11),""))</f>
         <v/>
       </c>
     </row>

--- a/dashboard-builder/Bluefield-Example-Inputs.xlsx
+++ b/dashboard-builder/Bluefield-Example-Inputs.xlsx
@@ -1658,11 +1658,11 @@
         </is>
       </c>
       <c r="B32" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Decimals in the page 2 cash flow table.</t>
+          <t xml:space="preserve">Decimals in the page 2 cash flow table and reserves (default 1).</t>
         </is>
       </c>
     </row>

--- a/dashboard-builder/Bluefield-Example-Inputs.xlsx
+++ b/dashboard-builder/Bluefield-Example-Inputs.xlsx
@@ -1609,7 +1609,7 @@
         </is>
       </c>
       <c r="B29" s="8">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>

--- a/dashboard-builder/Bluefield-Example-Inputs.xlsx
+++ b/dashboard-builder/Bluefield-Example-Inputs.xlsx
@@ -2882,67 +2882,67 @@
         </is>
       </c>
       <c r="C6" s="15">
-        <f>IF(COUNT(C2:C3,C4:C5,C9:C10)=0,"",SUM(C4:C5))</f>
+        <f>IF(COUNT(C2:C3,C4:C5,C9:C12)=0,"",SUM(C4:C5))</f>
         <v>2.33</v>
       </c>
       <c r="D6" s="15">
-        <f>IF(COUNT(D2:D3,D4:D5,D9:D10)=0,"",SUM(D4:D5))</f>
+        <f>IF(COUNT(D2:D3,D4:D5,D9:D12)=0,"",SUM(D4:D5))</f>
         <v>2.5</v>
       </c>
       <c r="E6" s="15">
-        <f>IF(COUNT(E2:E3,E4:E5,E9:E10)=0,"",SUM(E4:E5))</f>
+        <f>IF(COUNT(E2:E3,E4:E5,E9:E12)=0,"",SUM(E4:E5))</f>
         <v>2.63</v>
       </c>
       <c r="F6" s="15">
-        <f>IF(COUNT(F2:F3,F4:F5,F9:F10)=0,"",SUM(F4:F5))</f>
+        <f>IF(COUNT(F2:F3,F4:F5,F9:F12)=0,"",SUM(F4:F5))</f>
         <v>2.43</v>
       </c>
       <c r="G6" s="15">
-        <f>IF(COUNT(G2:G3,G4:G5,G9:G10)=0,"",SUM(G4:G5))</f>
+        <f>IF(COUNT(G2:G3,G4:G5,G9:G12)=0,"",SUM(G4:G5))</f>
         <v>2.5</v>
       </c>
       <c r="H6" s="15">
-        <f>IF(COUNT(H2:H3,H4:H5,H9:H10)=0,"",SUM(H4:H5))</f>
+        <f>IF(COUNT(H2:H3,H4:H5,H9:H12)=0,"",SUM(H4:H5))</f>
         <v>2.66</v>
       </c>
       <c r="I6" s="15">
-        <f>IF(COUNT(I2:I3,I4:I5,I9:I10)=0,"",SUM(I4:I5))</f>
+        <f>IF(COUNT(I2:I3,I4:I5,I9:I12)=0,"",SUM(I4:I5))</f>
         <v>2.78</v>
       </c>
       <c r="J6" s="15">
-        <f>IF(COUNT(J2:J3,J4:J5,J9:J10)=0,"",SUM(J4:J5))</f>
+        <f>IF(COUNT(J2:J3,J4:J5,J9:J12)=0,"",SUM(J4:J5))</f>
         <v>2.55</v>
       </c>
       <c r="K6" s="15">
-        <f>IF(COUNT(K2:K3,K4:K5,K9:K10)=0,"",SUM(K4:K5))</f>
+        <f>IF(COUNT(K2:K3,K4:K5,K9:K12)=0,"",SUM(K4:K5))</f>
         <v>2.64</v>
       </c>
       <c r="L6" s="15">
-        <f>IF(COUNT(L2:L3,L4:L5,L9:L10)=0,"",SUM(L4:L5))</f>
+        <f>IF(COUNT(L2:L3,L4:L5,L9:L12)=0,"",SUM(L4:L5))</f>
         <v>2.83</v>
       </c>
       <c r="M6" s="15">
-        <f>IF(COUNT(M2:M3,M4:M5,M9:M10)=0,"",SUM(M4:M5))</f>
+        <f>IF(COUNT(M2:M3,M4:M5,M9:M12)=0,"",SUM(M4:M5))</f>
         <v>2.91</v>
       </c>
       <c r="N6" s="15" t="str">
-        <f>IF(COUNT(N2:N3,N4:N5,N9:N10)=0,"",SUM(N4:N5))</f>
+        <f>IF(COUNT(N2:N3,N4:N5,N9:N12)=0,"",SUM(N4:N5))</f>
         <v/>
       </c>
       <c r="O6" s="15" t="str">
-        <f>IF(COUNT(O2:O3,O4:O5,O9:O10)=0,"",SUM(O4:O5))</f>
+        <f>IF(COUNT(O2:O3,O4:O5,O9:O12)=0,"",SUM(O4:O5))</f>
         <v/>
       </c>
       <c r="P6" s="15" t="str">
-        <f>IF(COUNT(P2:P3,P4:P5,P9:P10)=0,"",SUM(P4:P5))</f>
+        <f>IF(COUNT(P2:P3,P4:P5,P9:P12)=0,"",SUM(P4:P5))</f>
         <v/>
       </c>
       <c r="Q6" s="15" t="str">
-        <f>IF(COUNT(Q2:Q3,Q4:Q5,Q9:Q10)=0,"",SUM(Q4:Q5))</f>
+        <f>IF(COUNT(Q2:Q3,Q4:Q5,Q9:Q12)=0,"",SUM(Q4:Q5))</f>
         <v/>
       </c>
       <c r="R6" s="15" t="str">
-        <f>IF(COUNT(R2:R3,R4:R5,R9:R10)=0,"",SUM(R4:R5))</f>
+        <f>IF(COUNT(R2:R3,R4:R5,R9:R12)=0,"",SUM(R4:R5))</f>
         <v/>
       </c>
     </row>
@@ -2958,67 +2958,67 @@
         </is>
       </c>
       <c r="C7" s="15">
-        <f>IF(COUNT(C2:C3,C4:C5,C9:C10)=0,"",SUM(C2:C3)-C6)</f>
+        <f>IF(COUNT(C2:C3,C4:C5,C9:C12)=0,"",SUM(C2:C3)-C6)</f>
         <v>3.09</v>
       </c>
       <c r="D7" s="15">
-        <f>IF(COUNT(D2:D3,D4:D5,D9:D10)=0,"",SUM(D2:D3)-D6)</f>
+        <f>IF(COUNT(D2:D3,D4:D5,D9:D12)=0,"",SUM(D2:D3)-D6)</f>
         <v>7.28</v>
       </c>
       <c r="E7" s="15">
-        <f>IF(COUNT(E2:E3,E4:E5,E9:E10)=0,"",SUM(E2:E3)-E6)</f>
+        <f>IF(COUNT(E2:E3,E4:E5,E9:E12)=0,"",SUM(E2:E3)-E6)</f>
         <v>7.58</v>
       </c>
       <c r="F7" s="15">
-        <f>IF(COUNT(F2:F3,F4:F5,F9:F10)=0,"",SUM(F2:F3)-F6)</f>
+        <f>IF(COUNT(F2:F3,F4:F5,F9:F12)=0,"",SUM(F2:F3)-F6)</f>
         <v>2.88</v>
       </c>
       <c r="G7" s="15">
-        <f>IF(COUNT(G2:G3,G4:G5,G9:G10)=0,"",SUM(G2:G3)-G6)</f>
+        <f>IF(COUNT(G2:G3,G4:G5,G9:G12)=0,"",SUM(G2:G3)-G6)</f>
         <v>3.12</v>
       </c>
       <c r="H7" s="15">
-        <f>IF(COUNT(H2:H3,H4:H5,H9:H10)=0,"",SUM(H2:H3)-H6)</f>
+        <f>IF(COUNT(H2:H3,H4:H5,H9:H12)=0,"",SUM(H2:H3)-H6)</f>
         <v>7.38</v>
       </c>
       <c r="I7" s="15">
-        <f>IF(COUNT(I2:I3,I4:I5,I9:I10)=0,"",SUM(I2:I3)-I6)</f>
+        <f>IF(COUNT(I2:I3,I4:I5,I9:I12)=0,"",SUM(I2:I3)-I6)</f>
         <v>7.74</v>
       </c>
       <c r="J7" s="15">
-        <f>IF(COUNT(J2:J3,J4:J5,J9:J10)=0,"",SUM(J2:J3)-J6)</f>
+        <f>IF(COUNT(J2:J3,J4:J5,J9:J12)=0,"",SUM(J2:J3)-J6)</f>
         <v>3.38</v>
       </c>
       <c r="K7" s="15">
-        <f>IF(COUNT(K2:K3,K4:K5,K9:K10)=0,"",SUM(K2:K3)-K6)</f>
+        <f>IF(COUNT(K2:K3,K4:K5,K9:K12)=0,"",SUM(K2:K3)-K6)</f>
         <v>3.44</v>
       </c>
       <c r="L7" s="15">
-        <f>IF(COUNT(L2:L3,L4:L5,L9:L10)=0,"",SUM(L2:L3)-L6)</f>
+        <f>IF(COUNT(L2:L3,L4:L5,L9:L12)=0,"",SUM(L2:L3)-L6)</f>
         <v>7.78</v>
       </c>
       <c r="M7" s="15">
-        <f>IF(COUNT(M2:M3,M4:M5,M9:M10)=0,"",SUM(M2:M3)-M6)</f>
+        <f>IF(COUNT(M2:M3,M4:M5,M9:M12)=0,"",SUM(M2:M3)-M6)</f>
         <v>8.03</v>
       </c>
       <c r="N7" s="15" t="str">
-        <f>IF(COUNT(N2:N3,N4:N5,N9:N10)=0,"",SUM(N2:N3)-N6)</f>
+        <f>IF(COUNT(N2:N3,N4:N5,N9:N12)=0,"",SUM(N2:N3)-N6)</f>
         <v/>
       </c>
       <c r="O7" s="15" t="str">
-        <f>IF(COUNT(O2:O3,O4:O5,O9:O10)=0,"",SUM(O2:O3)-O6)</f>
+        <f>IF(COUNT(O2:O3,O4:O5,O9:O12)=0,"",SUM(O2:O3)-O6)</f>
         <v/>
       </c>
       <c r="P7" s="15" t="str">
-        <f>IF(COUNT(P2:P3,P4:P5,P9:P10)=0,"",SUM(P2:P3)-P6)</f>
+        <f>IF(COUNT(P2:P3,P4:P5,P9:P12)=0,"",SUM(P2:P3)-P6)</f>
         <v/>
       </c>
       <c r="Q7" s="15" t="str">
-        <f>IF(COUNT(Q2:Q3,Q4:Q5,Q9:Q10)=0,"",SUM(Q2:Q3)-Q6)</f>
+        <f>IF(COUNT(Q2:Q3,Q4:Q5,Q9:Q12)=0,"",SUM(Q2:Q3)-Q6)</f>
         <v/>
       </c>
       <c r="R7" s="15" t="str">
-        <f>IF(COUNT(R2:R3,R4:R5,R9:R10)=0,"",SUM(R2:R3)-R6)</f>
+        <f>IF(COUNT(R2:R3,R4:R5,R9:R12)=0,"",SUM(R2:R3)-R6)</f>
         <v/>
       </c>
     </row>
@@ -3124,231 +3124,331 @@
       <c r="R10" s="10"/>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Total debt service costs</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Calculated</t>
-        </is>
-      </c>
-      <c r="C11" s="15">
-        <f>IF(COUNT(C2:C3,C4:C5,C9:C10)=0,"",SUM(C9:C10))</f>
-        <v>4.35</v>
-      </c>
-      <c r="D11" s="15">
-        <f>IF(COUNT(D2:D3,D4:D5,D9:D10)=0,"",SUM(D9:D10))</f>
-        <v>4.33</v>
-      </c>
-      <c r="E11" s="15">
-        <f>IF(COUNT(E2:E3,E4:E5,E9:E10)=0,"",SUM(E9:E10))</f>
-        <v>4.32</v>
-      </c>
-      <c r="F11" s="15">
-        <f>IF(COUNT(F2:F3,F4:F5,F9:F10)=0,"",SUM(F9:F10))</f>
-        <v>4.31</v>
-      </c>
-      <c r="G11" s="15">
-        <f>IF(COUNT(G2:G3,G4:G5,G9:G10)=0,"",SUM(G9:G10))</f>
-        <v>4.28</v>
-      </c>
-      <c r="H11" s="15">
-        <f>IF(COUNT(H2:H3,H4:H5,H9:H10)=0,"",SUM(H9:H10))</f>
-        <v>4.29</v>
-      </c>
-      <c r="I11" s="15">
-        <f>IF(COUNT(I2:I3,I4:I5,I9:I10)=0,"",SUM(I9:I10))</f>
-        <v>4.27</v>
-      </c>
-      <c r="J11" s="15">
-        <f>IF(COUNT(J2:J3,J4:J5,J9:J10)=0,"",SUM(J9:J10))</f>
-        <v>4.27</v>
-      </c>
-      <c r="K11" s="15">
-        <f>IF(COUNT(K2:K3,K4:K5,K9:K10)=0,"",SUM(K9:K10))</f>
-        <v>4.27</v>
-      </c>
-      <c r="L11" s="15">
-        <f>IF(COUNT(L2:L3,L4:L5,L9:L10)=0,"",SUM(L9:L10))</f>
-        <v>4.28</v>
-      </c>
-      <c r="M11" s="15">
-        <f>IF(COUNT(M2:M3,M4:M5,M9:M10)=0,"",SUM(M9:M10))</f>
-        <v>4.29</v>
-      </c>
-      <c r="N11" s="15" t="str">
-        <f>IF(COUNT(N2:N3,N4:N5,N9:N10)=0,"",SUM(N9:N10))</f>
-        <v/>
-      </c>
-      <c r="O11" s="15" t="str">
-        <f>IF(COUNT(O2:O3,O4:O5,O9:O10)=0,"",SUM(O9:O10))</f>
-        <v/>
-      </c>
-      <c r="P11" s="15" t="str">
-        <f>IF(COUNT(P2:P3,P4:P5,P9:P10)=0,"",SUM(P9:P10))</f>
-        <v/>
-      </c>
-      <c r="Q11" s="15" t="str">
-        <f>IF(COUNT(Q2:Q3,Q4:Q5,Q9:Q10)=0,"",SUM(Q9:Q10))</f>
-        <v/>
-      </c>
-      <c r="R11" s="15" t="str">
-        <f>IF(COUNT(R2:R3,R4:R5,R9:R10)=0,"",SUM(R9:R10))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12"/>
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Interest rate swap settlements</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Debt service</t>
+        </is>
+      </c>
+      <c r="C11" s="10">
+        <v>0.06</v>
+      </c>
+      <c r="D11" s="10">
+        <v>0.05</v>
+      </c>
+      <c r="E11" s="10">
+        <v>0.04</v>
+      </c>
+      <c r="F11" s="10">
+        <v>0.03</v>
+      </c>
+      <c r="G11" s="10">
+        <v>0.02</v>
+      </c>
+      <c r="H11" s="10">
+        <v>0.01</v>
+      </c>
+      <c r="I11" s="10">
+        <v>-0.01</v>
+      </c>
+      <c r="J11" s="10">
+        <v>-0.02</v>
+      </c>
+      <c r="K11" s="10">
+        <v>-0.03</v>
+      </c>
+      <c r="L11" s="10">
+        <v>-0.02</v>
+      </c>
+      <c r="M11" s="10">
+        <v>-0.03</v>
+      </c>
+      <c r="N11" s="10"/>
+      <c r="O11" s="10"/>
+      <c r="P11" s="10"/>
+      <c r="Q11" s="10"/>
+      <c r="R11" s="10"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Agency fees</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Debt service</t>
+        </is>
+      </c>
+      <c r="C12" s="10">
+        <v>0.02</v>
+      </c>
+      <c r="D12" s="10">
+        <v>0.02</v>
+      </c>
+      <c r="E12" s="10">
+        <v>0.02</v>
+      </c>
+      <c r="F12" s="10">
+        <v>0.02</v>
+      </c>
+      <c r="G12" s="10">
+        <v>0.02</v>
+      </c>
+      <c r="H12" s="10">
+        <v>0.02</v>
+      </c>
+      <c r="I12" s="10">
+        <v>0.02</v>
+      </c>
+      <c r="J12" s="10">
+        <v>0.02</v>
+      </c>
+      <c r="K12" s="10">
+        <v>0.02</v>
+      </c>
+      <c r="L12" s="10">
+        <v>0.02</v>
+      </c>
+      <c r="M12" s="10">
+        <v>0.02</v>
+      </c>
+      <c r="N12" s="10"/>
+      <c r="O12" s="10"/>
+      <c r="P12" s="10"/>
+      <c r="Q12" s="10"/>
+      <c r="R12" s="10"/>
+    </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
+          <t xml:space="preserve">Total debt service costs</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Calculated</t>
+        </is>
+      </c>
+      <c r="C13" s="15">
+        <f>IF(COUNT(C2:C3,C4:C5,C9:C12)=0,"",SUM(C9:C12))</f>
+        <v>4.43</v>
+      </c>
+      <c r="D13" s="15">
+        <f>IF(COUNT(D2:D3,D4:D5,D9:D12)=0,"",SUM(D9:D12))</f>
+        <v>4.4</v>
+      </c>
+      <c r="E13" s="15">
+        <f>IF(COUNT(E2:E3,E4:E5,E9:E12)=0,"",SUM(E9:E12))</f>
+        <v>4.38</v>
+      </c>
+      <c r="F13" s="15">
+        <f>IF(COUNT(F2:F3,F4:F5,F9:F12)=0,"",SUM(F9:F12))</f>
+        <v>4.36</v>
+      </c>
+      <c r="G13" s="15">
+        <f>IF(COUNT(G2:G3,G4:G5,G9:G12)=0,"",SUM(G9:G12))</f>
+        <v>4.32</v>
+      </c>
+      <c r="H13" s="15">
+        <f>IF(COUNT(H2:H3,H4:H5,H9:H12)=0,"",SUM(H9:H12))</f>
+        <v>4.32</v>
+      </c>
+      <c r="I13" s="15">
+        <f>IF(COUNT(I2:I3,I4:I5,I9:I12)=0,"",SUM(I9:I12))</f>
+        <v>4.28</v>
+      </c>
+      <c r="J13" s="15">
+        <f>IF(COUNT(J2:J3,J4:J5,J9:J12)=0,"",SUM(J9:J12))</f>
+        <v>4.27</v>
+      </c>
+      <c r="K13" s="15">
+        <f>IF(COUNT(K2:K3,K4:K5,K9:K12)=0,"",SUM(K9:K12))</f>
+        <v>4.26</v>
+      </c>
+      <c r="L13" s="15">
+        <f>IF(COUNT(L2:L3,L4:L5,L9:L12)=0,"",SUM(L9:L12))</f>
+        <v>4.28</v>
+      </c>
+      <c r="M13" s="15">
+        <f>IF(COUNT(M2:M3,M4:M5,M9:M12)=0,"",SUM(M9:M12))</f>
+        <v>4.28</v>
+      </c>
+      <c r="N13" s="15" t="str">
+        <f>IF(COUNT(N2:N3,N4:N5,N9:N12)=0,"",SUM(N9:N12))</f>
+        <v/>
+      </c>
+      <c r="O13" s="15" t="str">
+        <f>IF(COUNT(O2:O3,O4:O5,O9:O12)=0,"",SUM(O9:O12))</f>
+        <v/>
+      </c>
+      <c r="P13" s="15" t="str">
+        <f>IF(COUNT(P2:P3,P4:P5,P9:P12)=0,"",SUM(P9:P12))</f>
+        <v/>
+      </c>
+      <c r="Q13" s="15" t="str">
+        <f>IF(COUNT(Q2:Q3,Q4:Q5,Q9:Q12)=0,"",SUM(Q9:Q12))</f>
+        <v/>
+      </c>
+      <c r="R13" s="15" t="str">
+        <f>IF(COUNT(R2:R3,R4:R5,R9:R12)=0,"",SUM(R9:R12))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
           <t xml:space="preserve">DSCR - quarter</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Calculated</t>
         </is>
       </c>
-      <c r="C13" s="16">
-        <f>IFERROR(C7/C11,"")</f>
-        <v>0.710345</v>
-      </c>
-      <c r="D13" s="16">
-        <f>IFERROR(D7/D11,"")</f>
-        <v>1.681293</v>
-      </c>
-      <c r="E13" s="16">
-        <f>IFERROR(E7/E11,"")</f>
-        <v>1.75463</v>
-      </c>
-      <c r="F13" s="16">
-        <f>IFERROR(F7/F11,"")</f>
-        <v>0.668213</v>
-      </c>
-      <c r="G13" s="16">
-        <f>IFERROR(G7/G11,"")</f>
-        <v>0.728972</v>
-      </c>
-      <c r="H13" s="16">
-        <f>IFERROR(H7/H11,"")</f>
-        <v>1.72028</v>
-      </c>
-      <c r="I13" s="16">
-        <f>IFERROR(I7/I11,"")</f>
-        <v>1.812646</v>
-      </c>
-      <c r="J13" s="16">
-        <f>IFERROR(J7/J11,"")</f>
+      <c r="C15" s="16">
+        <f>IFERROR(C7/C13,"")</f>
+        <v>0.697517</v>
+      </c>
+      <c r="D15" s="16">
+        <f>IFERROR(D7/D13,"")</f>
+        <v>1.654545</v>
+      </c>
+      <c r="E15" s="16">
+        <f>IFERROR(E7/E13,"")</f>
+        <v>1.730594</v>
+      </c>
+      <c r="F15" s="16">
+        <f>IFERROR(F7/F13,"")</f>
+        <v>0.66055</v>
+      </c>
+      <c r="G15" s="16">
+        <f>IFERROR(G7/G13,"")</f>
+        <v>0.722222</v>
+      </c>
+      <c r="H15" s="16">
+        <f>IFERROR(H7/H13,"")</f>
+        <v>1.708333</v>
+      </c>
+      <c r="I15" s="16">
+        <f>IFERROR(I7/I13,"")</f>
+        <v>1.808411</v>
+      </c>
+      <c r="J15" s="16">
+        <f>IFERROR(J7/J13,"")</f>
         <v>0.791569</v>
       </c>
-      <c r="K13" s="16">
-        <f>IFERROR(K7/K11,"")</f>
-        <v>0.805621</v>
-      </c>
-      <c r="L13" s="16">
-        <f>IFERROR(L7/L11,"")</f>
+      <c r="K15" s="16">
+        <f>IFERROR(K7/K13,"")</f>
+        <v>0.807512</v>
+      </c>
+      <c r="L15" s="16">
+        <f>IFERROR(L7/L13,"")</f>
         <v>1.817757</v>
       </c>
-      <c r="M13" s="16">
-        <f>IFERROR(M7/M11,"")</f>
-        <v>1.871795</v>
-      </c>
-      <c r="N13" s="16" t="str">
-        <f>IFERROR(N7/N11,"")</f>
-        <v/>
-      </c>
-      <c r="O13" s="16" t="str">
-        <f>IFERROR(O7/O11,"")</f>
-        <v/>
-      </c>
-      <c r="P13" s="16" t="str">
-        <f>IFERROR(P7/P11,"")</f>
-        <v/>
-      </c>
-      <c r="Q13" s="16" t="str">
-        <f>IFERROR(Q7/Q11,"")</f>
-        <v/>
-      </c>
-      <c r="R13" s="16" t="str">
-        <f>IFERROR(R7/R11,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="M15" s="16">
+        <f>IFERROR(M7/M13,"")</f>
+        <v>1.876168</v>
+      </c>
+      <c r="N15" s="16" t="str">
+        <f>IFERROR(N7/N13,"")</f>
+        <v/>
+      </c>
+      <c r="O15" s="16" t="str">
+        <f>IFERROR(O7/O13,"")</f>
+        <v/>
+      </c>
+      <c r="P15" s="16" t="str">
+        <f>IFERROR(P7/P13,"")</f>
+        <v/>
+      </c>
+      <c r="Q15" s="16" t="str">
+        <f>IFERROR(Q7/Q13,"")</f>
+        <v/>
+      </c>
+      <c r="R15" s="16" t="str">
+        <f>IFERROR(R7/R13,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">DSCR - LTM</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Calculated</t>
         </is>
       </c>
-      <c r="C14" s="16" t="str">
+      <c r="C16" s="16" t="str">
         <f>""</f>
         <v/>
       </c>
-      <c r="D14" s="16" t="str">
+      <c r="D16" s="16" t="str">
         <f>""</f>
         <v/>
       </c>
-      <c r="E14" s="16" t="str">
+      <c r="E16" s="16" t="str">
         <f>""</f>
         <v/>
       </c>
-      <c r="F14" s="16">
-        <f>IF(COUNT(C7:F7)&lt;4,"",IFERROR(SUM(C7:F7)/SUM(C11:F11),""))</f>
-        <v>1.203351</v>
-      </c>
-      <c r="G14" s="16">
-        <f>IF(COUNT(D7:G7)&lt;4,"",IFERROR(SUM(D7:G7)/SUM(D11:G11),""))</f>
-        <v>1.209977</v>
-      </c>
-      <c r="H14" s="16">
-        <f>IF(COUNT(E7:H7)&lt;4,"",IFERROR(SUM(E7:H7)/SUM(E11:H11),""))</f>
-        <v>1.218605</v>
-      </c>
-      <c r="I14" s="16">
-        <f>IF(COUNT(F7:I7)&lt;4,"",IFERROR(SUM(F7:I7)/SUM(F11:I11),""))</f>
-        <v>1.231487</v>
-      </c>
-      <c r="J14" s="16">
-        <f>IF(COUNT(G7:J7)&lt;4,"",IFERROR(SUM(G7:J7)/SUM(G11:J11),""))</f>
-        <v>1.263589</v>
-      </c>
-      <c r="K14" s="16">
-        <f>IF(COUNT(H7:K7)&lt;4,"",IFERROR(SUM(H7:K7)/SUM(H11:K11),""))</f>
-        <v>1.283041</v>
-      </c>
-      <c r="L14" s="16">
-        <f>IF(COUNT(I7:L7)&lt;4,"",IFERROR(SUM(I7:L7)/SUM(I11:L11),""))</f>
+      <c r="F16" s="16">
+        <f>IF(COUNT(C7:F7)&lt;4,"",IFERROR(SUM(C7:F7)/SUM(C13:F13),""))</f>
+        <v>1.185544</v>
+      </c>
+      <c r="G16" s="16">
+        <f>IF(COUNT(D7:G7)&lt;4,"",IFERROR(SUM(D7:G7)/SUM(D13:G13),""))</f>
+        <v>1.194731</v>
+      </c>
+      <c r="H16" s="16">
+        <f>IF(COUNT(E7:H7)&lt;4,"",IFERROR(SUM(E7:H7)/SUM(E13:H13),""))</f>
+        <v>1.205984</v>
+      </c>
+      <c r="I16" s="16">
+        <f>IF(COUNT(F7:I7)&lt;4,"",IFERROR(SUM(F7:I7)/SUM(F13:I13),""))</f>
+        <v>1.222222</v>
+      </c>
+      <c r="J16" s="16">
+        <f>IF(COUNT(G7:J7)&lt;4,"",IFERROR(SUM(G7:J7)/SUM(G13:J13),""))</f>
+        <v>1.257708</v>
+      </c>
+      <c r="K16" s="16">
+        <f>IF(COUNT(H7:K7)&lt;4,"",IFERROR(SUM(H7:K7)/SUM(H13:K13),""))</f>
+        <v>1.280794</v>
+      </c>
+      <c r="L16" s="16">
+        <f>IF(COUNT(I7:L7)&lt;4,"",IFERROR(SUM(I7:L7)/SUM(I13:L13),""))</f>
         <v>1.307197</v>
       </c>
-      <c r="M14" s="16">
-        <f>IF(COUNT(J7:M7)&lt;4,"",IFERROR(SUM(J7:M7)/SUM(J11:M11),""))</f>
-        <v>1.322618</v>
-      </c>
-      <c r="N14" s="16" t="str">
-        <f>IF(COUNT(K7:N7)&lt;4,"",IFERROR(SUM(K7:N7)/SUM(K11:N11),""))</f>
-        <v/>
-      </c>
-      <c r="O14" s="16" t="str">
-        <f>IF(COUNT(L7:O7)&lt;4,"",IFERROR(SUM(L7:O7)/SUM(L11:O11),""))</f>
-        <v/>
-      </c>
-      <c r="P14" s="16" t="str">
-        <f>IF(COUNT(M7:P7)&lt;4,"",IFERROR(SUM(M7:P7)/SUM(M11:P11),""))</f>
-        <v/>
-      </c>
-      <c r="Q14" s="16" t="str">
-        <f>IF(COUNT(N7:Q7)&lt;4,"",IFERROR(SUM(N7:Q7)/SUM(N11:Q11),""))</f>
-        <v/>
-      </c>
-      <c r="R14" s="16" t="str">
-        <f>IF(COUNT(O7:R7)&lt;4,"",IFERROR(SUM(O7:R7)/SUM(O11:R11),""))</f>
+      <c r="M16" s="16">
+        <f>IF(COUNT(J7:M7)&lt;4,"",IFERROR(SUM(J7:M7)/SUM(J13:M13),""))</f>
+        <v>1.324166</v>
+      </c>
+      <c r="N16" s="16" t="str">
+        <f>IF(COUNT(K7:N7)&lt;4,"",IFERROR(SUM(K7:N7)/SUM(K13:N13),""))</f>
+        <v/>
+      </c>
+      <c r="O16" s="16" t="str">
+        <f>IF(COUNT(L7:O7)&lt;4,"",IFERROR(SUM(L7:O7)/SUM(L13:O13),""))</f>
+        <v/>
+      </c>
+      <c r="P16" s="16" t="str">
+        <f>IF(COUNT(M7:P7)&lt;4,"",IFERROR(SUM(M7:P7)/SUM(M13:P13),""))</f>
+        <v/>
+      </c>
+      <c r="Q16" s="16" t="str">
+        <f>IF(COUNT(N7:Q7)&lt;4,"",IFERROR(SUM(N7:Q7)/SUM(N13:Q13),""))</f>
+        <v/>
+      </c>
+      <c r="R16" s="16" t="str">
+        <f>IF(COUNT(O7:R7)&lt;4,"",IFERROR(SUM(O7:R7)/SUM(O13:R13),""))</f>
         <v/>
       </c>
     </row>

--- a/dashboard-builder/Bluefield-Example-Inputs.xlsx
+++ b/dashboard-builder/Bluefield-Example-Inputs.xlsx
@@ -1903,34 +1903,34 @@
       <c r="D4" s="8">
         <v>1</v>
       </c>
-      <c r="E4" s="10">
+      <c r="E4" s="9">
         <v>1.62</v>
       </c>
-      <c r="F4" s="10">
+      <c r="F4" s="9">
         <v>1.84</v>
       </c>
-      <c r="G4" s="10">
+      <c r="G4" s="9">
         <v>2.57</v>
       </c>
-      <c r="H4" s="10">
+      <c r="H4" s="9">
         <v>3.03</v>
       </c>
-      <c r="I4" s="10">
+      <c r="I4" s="9">
         <v>3.41</v>
       </c>
-      <c r="J4" s="10">
+      <c r="J4" s="9">
         <v>4.12</v>
       </c>
-      <c r="K4" s="10">
+      <c r="K4" s="9">
         <v>3.46</v>
       </c>
-      <c r="L4" s="10">
+      <c r="L4" s="9">
         <v>3.92</v>
       </c>
-      <c r="M4" s="10"/>
-      <c r="N4" s="10"/>
-      <c r="O4" s="10"/>
-      <c r="P4" s="10"/>
+      <c r="M4" s="9"/>
+      <c r="N4" s="9"/>
+      <c r="O4" s="9"/>
+      <c r="P4" s="9"/>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
@@ -1995,34 +1995,34 @@
       <c r="D6" s="8">
         <v>1</v>
       </c>
-      <c r="E6" s="10">
+      <c r="E6" s="9">
         <v>-0.41</v>
       </c>
-      <c r="F6" s="10">
+      <c r="F6" s="9">
         <v>0.12</v>
       </c>
-      <c r="G6" s="10">
+      <c r="G6" s="9">
         <v>0.88</v>
       </c>
-      <c r="H6" s="10">
+      <c r="H6" s="9">
         <v>1.31</v>
       </c>
-      <c r="I6" s="10">
+      <c r="I6" s="9">
         <v>1.69</v>
       </c>
-      <c r="J6" s="10">
+      <c r="J6" s="9">
         <v>2.27</v>
       </c>
-      <c r="K6" s="10">
+      <c r="K6" s="9">
         <v>1.66</v>
       </c>
-      <c r="L6" s="10">
+      <c r="L6" s="9">
         <v>2.07</v>
       </c>
-      <c r="M6" s="10"/>
-      <c r="N6" s="10"/>
-      <c r="O6" s="10"/>
-      <c r="P6" s="10"/>
+      <c r="M6" s="9"/>
+      <c r="N6" s="9"/>
+      <c r="O6" s="9"/>
+      <c r="P6" s="9"/>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">

--- a/dashboard-builder/Bluefield-Example-Inputs.xlsx
+++ b/dashboard-builder/Bluefield-Example-Inputs.xlsx
@@ -2594,7 +2594,97 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Value</t>
+          <t xml:space="preserve">Balance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MoM</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unrestricted cash</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$1.2MM</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-$0.3MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">O&amp;M reserve</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$1.85MM</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">+$0.05MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Debt service reserve</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$8.62MM</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Flat</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Term loan</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$96.4MM</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-$0.9MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Revolver</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$0.0MM</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Flat</t>
         </is>
       </c>
     </row>

--- a/dashboard-builder/Bluefield-Example-Inputs.xlsx
+++ b/dashboard-builder/Bluefield-Example-Inputs.xlsx
@@ -258,209 +258,223 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">               Every chart shows the Prior year and Current year from Settings side by side, month by month.</t>
+          <t xml:space="preserve">               Every chart shows the Prior year and Current year from Settings side by side, month by month,</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">               Enter full precision here (e.g. 3.92); the Decimals column only controls how the chart labels are rounded.</t>
+          <t xml:space="preserve">               plus a YTD section on the right (Jan through Current month, both years).  "YTD Method": Sum (default),</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Footnotes  -  explain a month on a chart.  Pick the chart from the dropdown, or leave "Chart" blank to mark that month on every chart.</t>
+          <t xml:space="preserve">               Average (for percentages), or None to leave the YTD section off that chart.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">               The month label gets a small number and the note prints under the charts.</t>
+          <t xml:space="preserve">               Enter full precision here (e.g. 3.92); the Decimals column only controls how the chart labels are rounded.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Table  -  any number of rows.  The variance is calculated for you; "Better When" sets whether it shows green or red.</t>
+          <t xml:space="preserve">Footnotes  -  explain a month on a chart.  Pick the chart from the dropdown, or leave "Chart" blank to mark that month on every chart.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">               Month Actual and YTD Actual (black cells) are formulas: rows with a "From Chart" sum that chart on the Charts tab for the</t>
+          <t xml:space="preserve">               The month label gets a small number and the note prints under the charts.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">               Current year, for the Current month and Jan through it (add a "From Component" to use one component, e.g. Contracted).</t>
+          <t xml:space="preserve">Table  -  any number of rows.  The variance is calculated for you; "Better When" sets whether it shows green or red.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">               O&amp;M expense defaults to Revenue - Operating income.  Type a number over any formula to override it; the PDF uses the cell value.</t>
+          <t xml:space="preserve">               Month Actual and YTD Actual (black cells) are formulas: rows with a "From Chart" sum that chart on the Charts tab for the</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">               Rows with no "From Chart" and no formula: type the actuals yourself.</t>
+          <t xml:space="preserve">               Current year, for the Current month and Jan through it (add a "From Component" to use one component, e.g. Contracted).</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">               "EV Basis": if the EV Case values were pro-rated from quarterly, semi-annual or annual figures, pick that here.  The EV Case</t>
+          <t xml:space="preserve">               O&amp;M expense defaults to Revenue - Operating income.  Type a number over any formula to override it; the PDF uses the cell value.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">               values get a small letter (a, b, ...) and a footnote under the table explains it.  Monthly (the default) adds nothing.</t>
+          <t xml:space="preserve">               Rows with no "From Chart" and no formula: type the actuals yourself.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">               "YTD Method": Sum (default) adds the months up; Average averages them (use for percentages like capacity factor).</t>
+          <t xml:space="preserve">               "EV Basis": if the EV Case values were pro-rated from quarterly, semi-annual or annual figures, pick that here.  The EV Case</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">               Month EV Case and YTD EV Case are always typed in.</t>
+          <t xml:space="preserve">               values get a small letter (a, b, ...) and a footnote under the table explains it.  Monthly (the default) adds nothing.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commentary  -  Heading + Text pairs for the bottom-right box.</t>
+          <t xml:space="preserve">               "YTD Method": Sum (default) adds the months up; Average averages them (use for percentages like capacity factor).</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Side Table  -  a free-form grid for the bottom-right box.  Row 1 = column headers.  Values print exactly as they appear in Excel.</t>
+          <t xml:space="preserve">               Month EV Case and YTD EV Case are always typed in.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Debt Service  -  a running quarterly history for page 2: one column per quarter (Q1 2024 to Q4 2027).  Fill in each quarter when it closes;</t>
+          <t xml:space="preserve">Commentary  -  Heading + Text pairs for the bottom-right box.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">               nothing ever needs shifting.  Page 2 shows the last completed quarter before the Current month's quarter and the 3 before it</t>
+          <t xml:space="preserve">Side Table  -  a free-form grid for the bottom-right box.  Row 1 = column headers.  Values print exactly as they appear in Excel.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">               (Current month Aug -&gt; through Q2; Dec -&gt; through Q3).  Add more quarters by adding columns with labels like "Q1 2028".</t>
+          <t xml:space="preserve">Debt Service  -  a running quarterly history for page 2: one column per quarter (Q1 2024 to Q4 2027).  Fill in each quarter when it closes;</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">               Role: Revenue, Expense or Debt service.  Enter expenses and debt service as positive numbers.  The black "Calculated</t>
+          <t xml:space="preserve">               nothing ever needs shifting.  Page 2 shows the last completed quarter before the Current month's quarter and the 3 before it</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">               rows do the math: Total O&amp;M costs, CFADS = Revenue - Total O&amp;M costs, Total debt service costs, DSCR, and DSCR - LTM</t>
+          <t xml:space="preserve">               (Current month Aug -&gt; through Q2; Dec -&gt; through Q3).  Add more quarters by adding columns with labels like "Q1 2028".</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">               (last 4 quarters of CFADS / last 4 quarters of debt service).  To add a line (e.g. LC fees), insert the row between two</t>
+          <t xml:space="preserve">               Role: Revenue, Expense or Debt service.  Enter expenses and debt service as positive numbers.  The black "Calculated</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">               rows of the same block so the totals' ranges grow to include it.  The PDF recalculates from the input rows.</t>
+          <t xml:space="preserve">               rows do the math: Total O&amp;M costs, CFADS = Revenue - Total O&amp;M costs, Total debt service costs, DSCR, and DSCR - LTM</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reserves  -  one row per reserve account (DSR, O&amp;M reserve, ...): Required balance and Balance available.  Shown on page 2 below the DSCR chart</t>
+          <t xml:space="preserve">               (last 4 quarters of CFADS / last 4 quarters of debt service).  To add a line (e.g. LC fees), insert the row between two</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">               with the % funded; anything under 100% is flagged.</t>
+          <t xml:space="preserve">               rows of the same block so the totals' ranges grow to include it.  The PDF recalculates from the input rows.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t xml:space="preserve">Reserves  -  one row per reserve account (DSR, O&amp;M reserve, ...): Required balance and Balance available.  Shown on page 2 below the DSCR chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">               with the % funded; anything under 100% is flagged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t xml:space="preserve">DSCR Notes  -  optional Heading + Text pairs shown on page 2 below the reserves.</t>
         </is>
       </c>
     </row>
-    <row r="39"/>
-    <row r="40">
-      <c r="A40" s="6" t="inlineStr">
+    <row r="41"/>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Tips</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-  Do not rename the tabs or the column headers in row 1.  You can add, delete or reorder rows freely.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-  Copy this workbook for each asset (one workbook = one dashboard).</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">-  The Chart dropdowns list the names on the Charts tab automatically (from a hidden "Lists" tab).  Add a chart there and it appears in the dropdowns.</t>
+          <t xml:space="preserve">-  Do not rename the tabs or the column headers in row 1.  You can add, delete or reorder rows freely.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-  Copy this workbook for each asset (one workbook = one dashboard).</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-  The Chart dropdowns list the names on the Charts tab automatically (from a hidden "Lists" tab).  Add a chart there and it appears in the dropdowns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
         <is>
           <t xml:space="preserve">-  Your data never leaves your computer: the builder page reads the file locally in the browser.</t>
         </is>
@@ -1339,7 +1353,7 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Operating and Financial Performance vs. EV Case - Monthly &amp; YTD</t>
+          <t xml:space="preserve">Operating and Financial Performance vs. EV Case - YTD &amp; Monthly</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1714,6 +1728,7 @@
     <col min="14" max="14" width="8" customWidth="1"/>
     <col min="15" max="15" width="8" customWidth="1"/>
     <col min="16" max="16" width="8" customWidth="1"/>
+    <col min="17" max="17" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1797,6 +1812,11 @@
           <t xml:space="preserve">Dec</t>
         </is>
       </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YTD Method</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
@@ -1839,6 +1859,11 @@
       <c r="N2" s="9"/>
       <c r="O2" s="9"/>
       <c r="P2" s="9"/>
+      <c r="Q2" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sum</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
@@ -1888,6 +1913,11 @@
       </c>
       <c r="P3" s="9">
         <v>21.8</v>
+      </c>
+      <c r="Q3" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sum</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -1931,6 +1961,11 @@
       <c r="N4" s="9"/>
       <c r="O4" s="9"/>
       <c r="P4" s="9"/>
+      <c r="Q4" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sum</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
@@ -1980,6 +2015,11 @@
       </c>
       <c r="P5" s="9">
         <v>1.4</v>
+      </c>
+      <c r="Q5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sum</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -2023,6 +2063,11 @@
       <c r="N6" s="9"/>
       <c r="O6" s="9"/>
       <c r="P6" s="9"/>
+      <c r="Q6" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sum</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
@@ -2073,8 +2118,18 @@
       <c r="P7" s="9">
         <v>-0.5</v>
       </c>
+      <c r="Q7" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sum</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q500">
+      <formula1>"Sum,Average,None"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
